--- a/data/processed/recettes_produit.xlsx
+++ b/data/processed/recettes_produit.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:T165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,71 @@
           <t>date</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>trimestre</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lag_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lag_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lag_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>moyenne_mobile</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rolling_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_rolling_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_diff</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>trend</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E2" t="n">
         <v>20150</v>
@@ -494,7 +559,28 @@
         <v>357</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E3" t="n">
         <v>17800</v>
@@ -519,7 +605,34 @@
         <v>309</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20150</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +648,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E4" t="n">
         <v>19350</v>
@@ -544,7 +657,34 @@
         <v>317</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17800</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -560,7 +700,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E5" t="n">
         <v>15800</v>
@@ -569,7 +709,42 @@
         <v>274</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K5" t="n">
+        <v>19350</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20150</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>19100</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>327.6666666666667</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-43</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E6" t="n">
         <v>18600</v>
@@ -594,7 +769,42 @@
         <v>331</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15800</v>
+      </c>
+      <c r="L6" t="n">
+        <v>17800</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>17650</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>309</v>
+      </c>
+      <c r="R6" t="n">
+        <v>300</v>
+      </c>
+      <c r="S6" t="n">
+        <v>57</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -610,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E7" t="n">
         <v>12600</v>
@@ -619,7 +829,42 @@
         <v>228</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18600</v>
+      </c>
+      <c r="L7" t="n">
+        <v>19350</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>17916.66666666667</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>317</v>
+      </c>
+      <c r="R7" t="n">
+        <v>307.3333333333333</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-103</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +880,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E8" t="n">
         <v>9000</v>
@@ -644,7 +889,46 @@
         <v>158</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12600</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15800</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20150</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15666.66666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>17383.33333333333</v>
+      </c>
+      <c r="P8" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>274</v>
+      </c>
+      <c r="R8" t="n">
+        <v>277.6666666666667</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-70</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E9" t="n">
         <v>13900</v>
@@ -669,7 +953,46 @@
         <v>242</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18600</v>
+      </c>
+      <c r="M9" t="n">
+        <v>17800</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13400</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15525</v>
+      </c>
+      <c r="P9" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>331</v>
+      </c>
+      <c r="R9" t="n">
+        <v>239</v>
+      </c>
+      <c r="S9" t="n">
+        <v>84</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E10" t="n">
         <v>15600</v>
@@ -694,7 +1017,46 @@
         <v>280</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13900</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12600</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19350</v>
+      </c>
+      <c r="N10" t="n">
+        <v>11833.33333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>14875</v>
+      </c>
+      <c r="P10" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>228</v>
+      </c>
+      <c r="R10" t="n">
+        <v>209.3333333333333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +1072,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E11" t="n">
         <v>21350</v>
@@ -719,7 +1081,46 @@
         <v>375</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15800</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12833.33333333333</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14250</v>
+      </c>
+      <c r="P11" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>158</v>
+      </c>
+      <c r="R11" t="n">
+        <v>226.6666666666667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>95</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E12" t="n">
         <v>23350</v>
@@ -744,7 +1145,46 @@
         <v>390</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K12" t="n">
+        <v>21350</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M12" t="n">
+        <v>18600</v>
+      </c>
+      <c r="N12" t="n">
+        <v>16950</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15175</v>
+      </c>
+      <c r="P12" t="n">
+        <v>375</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>242</v>
+      </c>
+      <c r="R12" t="n">
+        <v>299</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -760,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E13" t="n">
         <v>16750</v>
@@ -769,7 +1209,46 @@
         <v>294</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23350</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12600</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20100</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15966.66666666667</v>
+      </c>
+      <c r="P13" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>280</v>
+      </c>
+      <c r="R13" t="n">
+        <v>348.3333333333333</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-96</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E14" t="n">
         <v>21900</v>
@@ -794,7 +1273,46 @@
         <v>378</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K14" t="n">
+        <v>16750</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21350</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20483.33333333333</v>
+      </c>
+      <c r="O14" t="n">
+        <v>16658.33333333333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>294</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>375</v>
+      </c>
+      <c r="R14" t="n">
+        <v>353</v>
+      </c>
+      <c r="S14" t="n">
+        <v>84</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +1328,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E15" t="n">
         <v>21850</v>
@@ -819,7 +1337,46 @@
         <v>373</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>21900</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23350</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13900</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20666.66666666667</v>
+      </c>
+      <c r="O15" t="n">
+        <v>18808.33333333333</v>
+      </c>
+      <c r="P15" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>390</v>
+      </c>
+      <c r="R15" t="n">
+        <v>354</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -835,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E16" t="n">
         <v>15250</v>
@@ -844,7 +1401,46 @@
         <v>256</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16750</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15600</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20166.66666666667</v>
+      </c>
+      <c r="O16" t="n">
+        <v>20133.33333333333</v>
+      </c>
+      <c r="P16" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>294</v>
+      </c>
+      <c r="R16" t="n">
+        <v>348.3333333333333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-117</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +1456,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E17" t="n">
         <v>17050</v>
@@ -869,7 +1465,46 @@
         <v>285</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15250</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21900</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21350</v>
+      </c>
+      <c r="N17" t="n">
+        <v>19666.66666666667</v>
+      </c>
+      <c r="O17" t="n">
+        <v>20075</v>
+      </c>
+      <c r="P17" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>378</v>
+      </c>
+      <c r="R17" t="n">
+        <v>335.6666666666667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -885,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E18" t="n">
         <v>19150</v>
@@ -894,7 +1529,46 @@
         <v>332</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K18" t="n">
+        <v>17050</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M18" t="n">
+        <v>23350</v>
+      </c>
+      <c r="N18" t="n">
+        <v>18050</v>
+      </c>
+      <c r="O18" t="n">
+        <v>19358.33333333333</v>
+      </c>
+      <c r="P18" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>373</v>
+      </c>
+      <c r="R18" t="n">
+        <v>304.6666666666667</v>
+      </c>
+      <c r="S18" t="n">
+        <v>47</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -910,7 +1584,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E19" t="n">
         <v>11150</v>
@@ -919,7 +1593,46 @@
         <v>183</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19150</v>
+      </c>
+      <c r="L19" t="n">
+        <v>15250</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16750</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17150</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18658.33333333333</v>
+      </c>
+      <c r="P19" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>256</v>
+      </c>
+      <c r="R19" t="n">
+        <v>291</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-149</v>
+      </c>
+      <c r="T19" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -935,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E20" t="n">
         <v>14000</v>
@@ -944,7 +1657,46 @@
         <v>242</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11150</v>
+      </c>
+      <c r="L20" t="n">
+        <v>17050</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21900</v>
+      </c>
+      <c r="N20" t="n">
+        <v>15783.33333333333</v>
+      </c>
+      <c r="O20" t="n">
+        <v>17725</v>
+      </c>
+      <c r="P20" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>285</v>
+      </c>
+      <c r="R20" t="n">
+        <v>266.6666666666667</v>
+      </c>
+      <c r="S20" t="n">
+        <v>59</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E21" t="n">
         <v>13950</v>
@@ -969,7 +1721,46 @@
         <v>237</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>19150</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21850</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14766.66666666667</v>
+      </c>
+      <c r="O21" t="n">
+        <v>16408.33333333333</v>
+      </c>
+      <c r="P21" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>332</v>
+      </c>
+      <c r="R21" t="n">
+        <v>252.3333333333333</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -985,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E22" t="n">
         <v>17750</v>
@@ -994,7 +1785,46 @@
         <v>302</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>13950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11150</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15250</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13033.33333333333</v>
+      </c>
+      <c r="O22" t="n">
+        <v>15091.66666666667</v>
+      </c>
+      <c r="P22" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>183</v>
+      </c>
+      <c r="R22" t="n">
+        <v>220.6666666666667</v>
+      </c>
+      <c r="S22" t="n">
+        <v>65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1010,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E23" t="n">
         <v>21100</v>
@@ -1019,7 +1849,46 @@
         <v>366</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K23" t="n">
+        <v>17750</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>17050</v>
+      </c>
+      <c r="N23" t="n">
+        <v>15233.33333333333</v>
+      </c>
+      <c r="O23" t="n">
+        <v>15508.33333333333</v>
+      </c>
+      <c r="P23" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>242</v>
+      </c>
+      <c r="R23" t="n">
+        <v>260.3333333333333</v>
+      </c>
+      <c r="S23" t="n">
+        <v>64</v>
+      </c>
+      <c r="T23" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1035,7 +1904,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E24" t="n">
         <v>18500</v>
@@ -1044,7 +1913,46 @@
         <v>315</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K24" t="n">
+        <v>21100</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13950</v>
+      </c>
+      <c r="M24" t="n">
+        <v>19150</v>
+      </c>
+      <c r="N24" t="n">
+        <v>17600</v>
+      </c>
+      <c r="O24" t="n">
+        <v>16183.33333333333</v>
+      </c>
+      <c r="P24" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>237</v>
+      </c>
+      <c r="R24" t="n">
+        <v>301.6666666666667</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-51</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1060,7 +1968,7 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E25" t="n">
         <v>19600</v>
@@ -1069,7 +1977,46 @@
         <v>329</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>18500</v>
+      </c>
+      <c r="L25" t="n">
+        <v>17750</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11150</v>
+      </c>
+      <c r="N25" t="n">
+        <v>19116.66666666667</v>
+      </c>
+      <c r="O25" t="n">
+        <v>16075</v>
+      </c>
+      <c r="P25" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>302</v>
+      </c>
+      <c r="R25" t="n">
+        <v>327.6666666666667</v>
+      </c>
+      <c r="S25" t="n">
+        <v>14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E26" t="n">
         <v>22250</v>
@@ -1094,7 +2041,46 @@
         <v>376</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K26" t="n">
+        <v>19600</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>14000</v>
+      </c>
+      <c r="N26" t="n">
+        <v>19733.33333333333</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17483.33333333333</v>
+      </c>
+      <c r="P26" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>366</v>
+      </c>
+      <c r="R26" t="n">
+        <v>336.6666666666667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>47</v>
+      </c>
+      <c r="T26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1110,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E27" t="n">
         <v>18500</v>
@@ -1119,7 +2105,46 @@
         <v>319</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>22250</v>
+      </c>
+      <c r="L27" t="n">
+        <v>18500</v>
+      </c>
+      <c r="M27" t="n">
+        <v>13950</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20116.66666666667</v>
+      </c>
+      <c r="O27" t="n">
+        <v>18858.33333333333</v>
+      </c>
+      <c r="P27" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>315</v>
+      </c>
+      <c r="R27" t="n">
+        <v>340</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-57</v>
+      </c>
+      <c r="T27" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1135,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E28" t="n">
         <v>16650</v>
@@ -1144,7 +2169,46 @@
         <v>277</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K28" t="n">
+        <v>18500</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19600</v>
+      </c>
+      <c r="M28" t="n">
+        <v>17750</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20116.66666666667</v>
+      </c>
+      <c r="O28" t="n">
+        <v>19616.66666666667</v>
+      </c>
+      <c r="P28" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>329</v>
+      </c>
+      <c r="R28" t="n">
+        <v>341.3333333333333</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-42</v>
+      </c>
+      <c r="T28" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1160,7 +2224,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E29" t="n">
         <v>21650</v>
@@ -1169,7 +2233,46 @@
         <v>357</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>16650</v>
+      </c>
+      <c r="L29" t="n">
+        <v>22250</v>
+      </c>
+      <c r="M29" t="n">
+        <v>21100</v>
+      </c>
+      <c r="N29" t="n">
+        <v>19133.33333333333</v>
+      </c>
+      <c r="O29" t="n">
+        <v>19433.33333333333</v>
+      </c>
+      <c r="P29" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>376</v>
+      </c>
+      <c r="R29" t="n">
+        <v>324</v>
+      </c>
+      <c r="S29" t="n">
+        <v>80</v>
+      </c>
+      <c r="T29" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1185,7 +2288,7 @@
         <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E30" t="n">
         <v>17300</v>
@@ -1194,7 +2297,46 @@
         <v>287</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K30" t="n">
+        <v>21650</v>
+      </c>
+      <c r="L30" t="n">
+        <v>18500</v>
+      </c>
+      <c r="M30" t="n">
+        <v>18500</v>
+      </c>
+      <c r="N30" t="n">
+        <v>18933.33333333333</v>
+      </c>
+      <c r="O30" t="n">
+        <v>19525</v>
+      </c>
+      <c r="P30" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>319</v>
+      </c>
+      <c r="R30" t="n">
+        <v>317.6666666666667</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-70</v>
+      </c>
+      <c r="T30" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1210,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E31" t="n">
         <v>13200</v>
@@ -1219,7 +2361,46 @@
         <v>224</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>17300</v>
+      </c>
+      <c r="L31" t="n">
+        <v>16650</v>
+      </c>
+      <c r="M31" t="n">
+        <v>19600</v>
+      </c>
+      <c r="N31" t="n">
+        <v>18533.33333333333</v>
+      </c>
+      <c r="O31" t="n">
+        <v>19325</v>
+      </c>
+      <c r="P31" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>277</v>
+      </c>
+      <c r="R31" t="n">
+        <v>307</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-63</v>
+      </c>
+      <c r="T31" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1235,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E32" t="n">
         <v>14400</v>
@@ -1244,7 +2425,46 @@
         <v>241</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K32" t="n">
+        <v>13200</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21650</v>
+      </c>
+      <c r="M32" t="n">
+        <v>22250</v>
+      </c>
+      <c r="N32" t="n">
+        <v>17383.33333333333</v>
+      </c>
+      <c r="O32" t="n">
+        <v>18258.33333333333</v>
+      </c>
+      <c r="P32" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>357</v>
+      </c>
+      <c r="R32" t="n">
+        <v>289.3333333333333</v>
+      </c>
+      <c r="S32" t="n">
+        <v>17</v>
+      </c>
+      <c r="T32" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1260,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E33" t="n">
         <v>13050</v>
@@ -1269,7 +2489,46 @@
         <v>230</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K33" t="n">
+        <v>14400</v>
+      </c>
+      <c r="L33" t="n">
+        <v>17300</v>
+      </c>
+      <c r="M33" t="n">
+        <v>18500</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14966.66666666667</v>
+      </c>
+      <c r="O33" t="n">
+        <v>16950</v>
+      </c>
+      <c r="P33" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>287</v>
+      </c>
+      <c r="R33" t="n">
+        <v>250.6666666666667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T33" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1285,7 +2544,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E34" t="n">
         <v>19900</v>
@@ -1294,7 +2553,46 @@
         <v>328</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K34" t="n">
+        <v>13050</v>
+      </c>
+      <c r="L34" t="n">
+        <v>13200</v>
+      </c>
+      <c r="M34" t="n">
+        <v>16650</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13550</v>
+      </c>
+      <c r="O34" t="n">
+        <v>16041.66666666667</v>
+      </c>
+      <c r="P34" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>224</v>
+      </c>
+      <c r="R34" t="n">
+        <v>231.6666666666667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>98</v>
+      </c>
+      <c r="T34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1310,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E35" t="n">
         <v>20050</v>
@@ -1319,7 +2617,46 @@
         <v>330</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K35" t="n">
+        <v>19900</v>
+      </c>
+      <c r="L35" t="n">
+        <v>14400</v>
+      </c>
+      <c r="M35" t="n">
+        <v>21650</v>
+      </c>
+      <c r="N35" t="n">
+        <v>15783.33333333333</v>
+      </c>
+      <c r="O35" t="n">
+        <v>16583.33333333333</v>
+      </c>
+      <c r="P35" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>241</v>
+      </c>
+      <c r="R35" t="n">
+        <v>266.3333333333333</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -1335,7 +2672,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E36" t="n">
         <v>18000</v>
@@ -1344,7 +2681,46 @@
         <v>312</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K36" t="n">
+        <v>20050</v>
+      </c>
+      <c r="L36" t="n">
+        <v>13050</v>
+      </c>
+      <c r="M36" t="n">
+        <v>17300</v>
+      </c>
+      <c r="N36" t="n">
+        <v>17666.66666666667</v>
+      </c>
+      <c r="O36" t="n">
+        <v>16316.66666666667</v>
+      </c>
+      <c r="P36" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>230</v>
+      </c>
+      <c r="R36" t="n">
+        <v>296</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-18</v>
+      </c>
+      <c r="T36" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -1360,7 +2736,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E37" t="n">
         <v>16200</v>
@@ -1369,7 +2745,46 @@
         <v>278</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>19900</v>
+      </c>
+      <c r="M37" t="n">
+        <v>13200</v>
+      </c>
+      <c r="N37" t="n">
+        <v>19316.66666666667</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16433.33333333333</v>
+      </c>
+      <c r="P37" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>328</v>
+      </c>
+      <c r="R37" t="n">
+        <v>323.3333333333333</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-34</v>
+      </c>
+      <c r="T37" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1385,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E38" t="n">
         <v>39600</v>
@@ -1394,7 +2809,28 @@
         <v>336</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +2846,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E39" t="n">
         <v>33300</v>
@@ -1419,7 +2855,34 @@
         <v>281</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K39" t="n">
+        <v>39600</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>-55</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +2898,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E40" t="n">
         <v>34900</v>
@@ -1444,7 +2907,34 @@
         <v>277</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K40" t="n">
+        <v>33300</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1460,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E41" t="n">
         <v>27800</v>
@@ -1469,7 +2959,42 @@
         <v>231</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K41" t="n">
+        <v>34900</v>
+      </c>
+      <c r="L41" t="n">
+        <v>39600</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>35933.33333333334</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>336</v>
+      </c>
+      <c r="R41" t="n">
+        <v>298</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-46</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E42" t="n">
         <v>34100</v>
@@ -1494,7 +3019,42 @@
         <v>283</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K42" t="n">
+        <v>27800</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33300</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>32000</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>281</v>
+      </c>
+      <c r="R42" t="n">
+        <v>263</v>
+      </c>
+      <c r="S42" t="n">
+        <v>52</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1510,7 +3070,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E43" t="n">
         <v>25200</v>
@@ -1519,7 +3079,42 @@
         <v>207</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>34100</v>
+      </c>
+      <c r="L43" t="n">
+        <v>34900</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>32266.66666666667</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>277</v>
+      </c>
+      <c r="R43" t="n">
+        <v>263.6666666666667</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-76</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +3130,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E44" t="n">
         <v>12500</v>
@@ -1544,7 +3139,46 @@
         <v>107</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K44" t="n">
+        <v>25200</v>
+      </c>
+      <c r="L44" t="n">
+        <v>27800</v>
+      </c>
+      <c r="M44" t="n">
+        <v>39600</v>
+      </c>
+      <c r="N44" t="n">
+        <v>29033.33333333333</v>
+      </c>
+      <c r="O44" t="n">
+        <v>32483.33333333333</v>
+      </c>
+      <c r="P44" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>231</v>
+      </c>
+      <c r="R44" t="n">
+        <v>240.3333333333333</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -1560,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E45" t="n">
         <v>20000</v>
@@ -1569,7 +3203,46 @@
         <v>175</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12500</v>
+      </c>
+      <c r="L45" t="n">
+        <v>34100</v>
+      </c>
+      <c r="M45" t="n">
+        <v>33300</v>
+      </c>
+      <c r="N45" t="n">
+        <v>23933.33333333333</v>
+      </c>
+      <c r="O45" t="n">
+        <v>27966.66666666667</v>
+      </c>
+      <c r="P45" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>283</v>
+      </c>
+      <c r="R45" t="n">
+        <v>199</v>
+      </c>
+      <c r="S45" t="n">
+        <v>68</v>
+      </c>
+      <c r="T45" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1585,7 +3258,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E46" t="n">
         <v>26900</v>
@@ -1594,7 +3267,46 @@
         <v>238</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>25200</v>
+      </c>
+      <c r="M46" t="n">
+        <v>34900</v>
+      </c>
+      <c r="N46" t="n">
+        <v>19233.33333333333</v>
+      </c>
+      <c r="O46" t="n">
+        <v>25750</v>
+      </c>
+      <c r="P46" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>207</v>
+      </c>
+      <c r="R46" t="n">
+        <v>163</v>
+      </c>
+      <c r="S46" t="n">
+        <v>63</v>
+      </c>
+      <c r="T46" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1610,7 +3322,7 @@
         <v>10</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E47" t="n">
         <v>37000</v>
@@ -1619,7 +3331,46 @@
         <v>311</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K47" t="n">
+        <v>26900</v>
+      </c>
+      <c r="L47" t="n">
+        <v>12500</v>
+      </c>
+      <c r="M47" t="n">
+        <v>27800</v>
+      </c>
+      <c r="N47" t="n">
+        <v>19800</v>
+      </c>
+      <c r="O47" t="n">
+        <v>24416.66666666667</v>
+      </c>
+      <c r="P47" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>107</v>
+      </c>
+      <c r="R47" t="n">
+        <v>173.3333333333333</v>
+      </c>
+      <c r="S47" t="n">
+        <v>73</v>
+      </c>
+      <c r="T47" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -1635,7 +3386,7 @@
         <v>11</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E48" t="n">
         <v>40600</v>
@@ -1644,7 +3395,46 @@
         <v>332</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K48" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L48" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M48" t="n">
+        <v>34100</v>
+      </c>
+      <c r="N48" t="n">
+        <v>27966.66666666667</v>
+      </c>
+      <c r="O48" t="n">
+        <v>25950</v>
+      </c>
+      <c r="P48" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>175</v>
+      </c>
+      <c r="R48" t="n">
+        <v>241.3333333333333</v>
+      </c>
+      <c r="S48" t="n">
+        <v>21</v>
+      </c>
+      <c r="T48" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -1660,7 +3450,7 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E49" t="n">
         <v>31100</v>
@@ -1669,7 +3459,46 @@
         <v>259</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>40600</v>
+      </c>
+      <c r="L49" t="n">
+        <v>26900</v>
+      </c>
+      <c r="M49" t="n">
+        <v>25200</v>
+      </c>
+      <c r="N49" t="n">
+        <v>34833.33333333334</v>
+      </c>
+      <c r="O49" t="n">
+        <v>27033.33333333333</v>
+      </c>
+      <c r="P49" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>238</v>
+      </c>
+      <c r="R49" t="n">
+        <v>293.6666666666667</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-73</v>
+      </c>
+      <c r="T49" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -1685,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E50" t="n">
         <v>39200</v>
@@ -1694,7 +3523,46 @@
         <v>323</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K50" t="n">
+        <v>31100</v>
+      </c>
+      <c r="L50" t="n">
+        <v>37000</v>
+      </c>
+      <c r="M50" t="n">
+        <v>12500</v>
+      </c>
+      <c r="N50" t="n">
+        <v>36233.33333333334</v>
+      </c>
+      <c r="O50" t="n">
+        <v>28016.66666666667</v>
+      </c>
+      <c r="P50" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>311</v>
+      </c>
+      <c r="R50" t="n">
+        <v>300.6666666666667</v>
+      </c>
+      <c r="S50" t="n">
+        <v>64</v>
+      </c>
+      <c r="T50" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -1710,7 +3578,7 @@
         <v>2</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E51" t="n">
         <v>38300</v>
@@ -1719,7 +3587,46 @@
         <v>317</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K51" t="n">
+        <v>39200</v>
+      </c>
+      <c r="L51" t="n">
+        <v>40600</v>
+      </c>
+      <c r="M51" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N51" t="n">
+        <v>36966.66666666666</v>
+      </c>
+      <c r="O51" t="n">
+        <v>32466.66666666667</v>
+      </c>
+      <c r="P51" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>332</v>
+      </c>
+      <c r="R51" t="n">
+        <v>304.6666666666667</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T51" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -1735,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E52" t="n">
         <v>25700</v>
@@ -1744,7 +3651,46 @@
         <v>210</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K52" t="n">
+        <v>38300</v>
+      </c>
+      <c r="L52" t="n">
+        <v>31100</v>
+      </c>
+      <c r="M52" t="n">
+        <v>26900</v>
+      </c>
+      <c r="N52" t="n">
+        <v>36200</v>
+      </c>
+      <c r="O52" t="n">
+        <v>35516.66666666666</v>
+      </c>
+      <c r="P52" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>259</v>
+      </c>
+      <c r="R52" t="n">
+        <v>299.6666666666667</v>
+      </c>
+      <c r="S52" t="n">
+        <v>-107</v>
+      </c>
+      <c r="T52" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -1760,7 +3706,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E53" t="n">
         <v>27600</v>
@@ -1769,7 +3715,46 @@
         <v>228</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K53" t="n">
+        <v>25700</v>
+      </c>
+      <c r="L53" t="n">
+        <v>39200</v>
+      </c>
+      <c r="M53" t="n">
+        <v>37000</v>
+      </c>
+      <c r="N53" t="n">
+        <v>34400</v>
+      </c>
+      <c r="O53" t="n">
+        <v>35316.66666666666</v>
+      </c>
+      <c r="P53" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>323</v>
+      </c>
+      <c r="R53" t="n">
+        <v>283.3333333333333</v>
+      </c>
+      <c r="S53" t="n">
+        <v>18</v>
+      </c>
+      <c r="T53" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -1785,7 +3770,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E54" t="n">
         <v>32200</v>
@@ -1794,7 +3779,46 @@
         <v>265</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K54" t="n">
+        <v>27600</v>
+      </c>
+      <c r="L54" t="n">
+        <v>38300</v>
+      </c>
+      <c r="M54" t="n">
+        <v>40600</v>
+      </c>
+      <c r="N54" t="n">
+        <v>30533.33333333333</v>
+      </c>
+      <c r="O54" t="n">
+        <v>33750</v>
+      </c>
+      <c r="P54" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>317</v>
+      </c>
+      <c r="R54" t="n">
+        <v>251.6666666666667</v>
+      </c>
+      <c r="S54" t="n">
+        <v>37</v>
+      </c>
+      <c r="T54" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -1810,7 +3834,7 @@
         <v>6</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E55" t="n">
         <v>18400</v>
@@ -1819,7 +3843,46 @@
         <v>147</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>32200</v>
+      </c>
+      <c r="L55" t="n">
+        <v>25700</v>
+      </c>
+      <c r="M55" t="n">
+        <v>31100</v>
+      </c>
+      <c r="N55" t="n">
+        <v>28500</v>
+      </c>
+      <c r="O55" t="n">
+        <v>32350</v>
+      </c>
+      <c r="P55" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>210</v>
+      </c>
+      <c r="R55" t="n">
+        <v>234.3333333333333</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-118</v>
+      </c>
+      <c r="T55" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -1835,7 +3898,7 @@
         <v>7</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E56" t="n">
         <v>23600</v>
@@ -1844,7 +3907,46 @@
         <v>204</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K56" t="n">
+        <v>18400</v>
+      </c>
+      <c r="L56" t="n">
+        <v>27600</v>
+      </c>
+      <c r="M56" t="n">
+        <v>39200</v>
+      </c>
+      <c r="N56" t="n">
+        <v>26066.66666666667</v>
+      </c>
+      <c r="O56" t="n">
+        <v>30233.33333333333</v>
+      </c>
+      <c r="P56" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>228</v>
+      </c>
+      <c r="R56" t="n">
+        <v>213.3333333333333</v>
+      </c>
+      <c r="S56" t="n">
+        <v>57</v>
+      </c>
+      <c r="T56" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -1860,7 +3962,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E57" t="n">
         <v>23700</v>
@@ -1869,7 +3971,46 @@
         <v>198</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K57" t="n">
+        <v>23600</v>
+      </c>
+      <c r="L57" t="n">
+        <v>32200</v>
+      </c>
+      <c r="M57" t="n">
+        <v>38300</v>
+      </c>
+      <c r="N57" t="n">
+        <v>24733.33333333333</v>
+      </c>
+      <c r="O57" t="n">
+        <v>27633.33333333333</v>
+      </c>
+      <c r="P57" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>265</v>
+      </c>
+      <c r="R57" t="n">
+        <v>205.3333333333333</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T57" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="58">
@@ -1885,7 +4026,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E58" t="n">
         <v>28600</v>
@@ -1894,7 +4035,46 @@
         <v>242</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23700</v>
+      </c>
+      <c r="L58" t="n">
+        <v>18400</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25700</v>
+      </c>
+      <c r="N58" t="n">
+        <v>21900</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25200</v>
+      </c>
+      <c r="P58" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>147</v>
+      </c>
+      <c r="R58" t="n">
+        <v>183</v>
+      </c>
+      <c r="S58" t="n">
+        <v>44</v>
+      </c>
+      <c r="T58" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -1910,7 +4090,7 @@
         <v>10</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E59" t="n">
         <v>38300</v>
@@ -1919,7 +4099,46 @@
         <v>325</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K59" t="n">
+        <v>28600</v>
+      </c>
+      <c r="L59" t="n">
+        <v>23600</v>
+      </c>
+      <c r="M59" t="n">
+        <v>27600</v>
+      </c>
+      <c r="N59" t="n">
+        <v>25300</v>
+      </c>
+      <c r="O59" t="n">
+        <v>25683.33333333333</v>
+      </c>
+      <c r="P59" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>204</v>
+      </c>
+      <c r="R59" t="n">
+        <v>214.6666666666667</v>
+      </c>
+      <c r="S59" t="n">
+        <v>83</v>
+      </c>
+      <c r="T59" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="60">
@@ -1935,7 +4154,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E60" t="n">
         <v>29700</v>
@@ -1944,7 +4163,46 @@
         <v>255</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K60" t="n">
+        <v>38300</v>
+      </c>
+      <c r="L60" t="n">
+        <v>23700</v>
+      </c>
+      <c r="M60" t="n">
+        <v>32200</v>
+      </c>
+      <c r="N60" t="n">
+        <v>30200</v>
+      </c>
+      <c r="O60" t="n">
+        <v>27466.66666666667</v>
+      </c>
+      <c r="P60" t="n">
+        <v>325</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>198</v>
+      </c>
+      <c r="R60" t="n">
+        <v>255</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-70</v>
+      </c>
+      <c r="T60" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -1960,7 +4218,7 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E61" t="n">
         <v>32900</v>
@@ -1969,7 +4227,46 @@
         <v>273</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>29700</v>
+      </c>
+      <c r="L61" t="n">
+        <v>28600</v>
+      </c>
+      <c r="M61" t="n">
+        <v>18400</v>
+      </c>
+      <c r="N61" t="n">
+        <v>32200</v>
+      </c>
+      <c r="O61" t="n">
+        <v>27050</v>
+      </c>
+      <c r="P61" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>242</v>
+      </c>
+      <c r="R61" t="n">
+        <v>274</v>
+      </c>
+      <c r="S61" t="n">
+        <v>18</v>
+      </c>
+      <c r="T61" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="62">
@@ -1985,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E62" t="n">
         <v>46200</v>
@@ -1994,7 +4291,46 @@
         <v>365</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K62" t="n">
+        <v>32900</v>
+      </c>
+      <c r="L62" t="n">
+        <v>38300</v>
+      </c>
+      <c r="M62" t="n">
+        <v>23600</v>
+      </c>
+      <c r="N62" t="n">
+        <v>33633.33333333334</v>
+      </c>
+      <c r="O62" t="n">
+        <v>29466.66666666667</v>
+      </c>
+      <c r="P62" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>325</v>
+      </c>
+      <c r="R62" t="n">
+        <v>284.3333333333333</v>
+      </c>
+      <c r="S62" t="n">
+        <v>92</v>
+      </c>
+      <c r="T62" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -2010,7 +4346,7 @@
         <v>2</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E63" t="n">
         <v>33100</v>
@@ -2019,7 +4355,46 @@
         <v>276</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K63" t="n">
+        <v>46200</v>
+      </c>
+      <c r="L63" t="n">
+        <v>29700</v>
+      </c>
+      <c r="M63" t="n">
+        <v>23700</v>
+      </c>
+      <c r="N63" t="n">
+        <v>36266.66666666666</v>
+      </c>
+      <c r="O63" t="n">
+        <v>33233.33333333334</v>
+      </c>
+      <c r="P63" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>255</v>
+      </c>
+      <c r="R63" t="n">
+        <v>297.6666666666667</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-89</v>
+      </c>
+      <c r="T63" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="64">
@@ -2035,7 +4410,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E64" t="n">
         <v>28200</v>
@@ -2044,7 +4419,46 @@
         <v>227</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K64" t="n">
+        <v>33100</v>
+      </c>
+      <c r="L64" t="n">
+        <v>32900</v>
+      </c>
+      <c r="M64" t="n">
+        <v>28600</v>
+      </c>
+      <c r="N64" t="n">
+        <v>37400</v>
+      </c>
+      <c r="O64" t="n">
+        <v>34800</v>
+      </c>
+      <c r="P64" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>273</v>
+      </c>
+      <c r="R64" t="n">
+        <v>304.6666666666667</v>
+      </c>
+      <c r="S64" t="n">
+        <v>-49</v>
+      </c>
+      <c r="T64" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -2060,7 +4474,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E65" t="n">
         <v>38000</v>
@@ -2069,7 +4483,46 @@
         <v>299</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K65" t="n">
+        <v>28200</v>
+      </c>
+      <c r="L65" t="n">
+        <v>46200</v>
+      </c>
+      <c r="M65" t="n">
+        <v>38300</v>
+      </c>
+      <c r="N65" t="n">
+        <v>35833.33333333334</v>
+      </c>
+      <c r="O65" t="n">
+        <v>34733.33333333334</v>
+      </c>
+      <c r="P65" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>365</v>
+      </c>
+      <c r="R65" t="n">
+        <v>289.3333333333333</v>
+      </c>
+      <c r="S65" t="n">
+        <v>72</v>
+      </c>
+      <c r="T65" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="66">
@@ -2085,7 +4538,7 @@
         <v>5</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E66" t="n">
         <v>31200</v>
@@ -2094,7 +4547,46 @@
         <v>247</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K66" t="n">
+        <v>38000</v>
+      </c>
+      <c r="L66" t="n">
+        <v>33100</v>
+      </c>
+      <c r="M66" t="n">
+        <v>29700</v>
+      </c>
+      <c r="N66" t="n">
+        <v>33100</v>
+      </c>
+      <c r="O66" t="n">
+        <v>34683.33333333334</v>
+      </c>
+      <c r="P66" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>276</v>
+      </c>
+      <c r="R66" t="n">
+        <v>267.3333333333333</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-52</v>
+      </c>
+      <c r="T66" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="67">
@@ -2110,7 +4602,7 @@
         <v>6</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E67" t="n">
         <v>20800</v>
@@ -2119,7 +4611,46 @@
         <v>168</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>31200</v>
+      </c>
+      <c r="L67" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M67" t="n">
+        <v>32900</v>
+      </c>
+      <c r="N67" t="n">
+        <v>32466.66666666667</v>
+      </c>
+      <c r="O67" t="n">
+        <v>34933.33333333334</v>
+      </c>
+      <c r="P67" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>227</v>
+      </c>
+      <c r="R67" t="n">
+        <v>257.6666666666667</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-79</v>
+      </c>
+      <c r="T67" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="68">
@@ -2135,7 +4666,7 @@
         <v>7</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E68" t="n">
         <v>24300</v>
@@ -2144,7 +4675,46 @@
         <v>195</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K68" t="n">
+        <v>20800</v>
+      </c>
+      <c r="L68" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M68" t="n">
+        <v>46200</v>
+      </c>
+      <c r="N68" t="n">
+        <v>30000</v>
+      </c>
+      <c r="O68" t="n">
+        <v>32916.66666666666</v>
+      </c>
+      <c r="P68" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>299</v>
+      </c>
+      <c r="R68" t="n">
+        <v>238</v>
+      </c>
+      <c r="S68" t="n">
+        <v>27</v>
+      </c>
+      <c r="T68" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -2160,7 +4730,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E69" t="n">
         <v>20900</v>
@@ -2169,7 +4739,46 @@
         <v>175</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K69" t="n">
+        <v>24300</v>
+      </c>
+      <c r="L69" t="n">
+        <v>31200</v>
+      </c>
+      <c r="M69" t="n">
+        <v>33100</v>
+      </c>
+      <c r="N69" t="n">
+        <v>25433.33333333333</v>
+      </c>
+      <c r="O69" t="n">
+        <v>29266.66666666667</v>
+      </c>
+      <c r="P69" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>247</v>
+      </c>
+      <c r="R69" t="n">
+        <v>203.3333333333333</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-20</v>
+      </c>
+      <c r="T69" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="70">
@@ -2185,7 +4794,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E70" t="n">
         <v>29500</v>
@@ -2194,7 +4803,46 @@
         <v>233</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K70" t="n">
+        <v>20900</v>
+      </c>
+      <c r="L70" t="n">
+        <v>20800</v>
+      </c>
+      <c r="M70" t="n">
+        <v>28200</v>
+      </c>
+      <c r="N70" t="n">
+        <v>22000</v>
+      </c>
+      <c r="O70" t="n">
+        <v>27233.33333333333</v>
+      </c>
+      <c r="P70" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>168</v>
+      </c>
+      <c r="R70" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="S70" t="n">
+        <v>58</v>
+      </c>
+      <c r="T70" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -2210,7 +4858,7 @@
         <v>10</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E71" t="n">
         <v>35000</v>
@@ -2219,7 +4867,46 @@
         <v>283</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K71" t="n">
+        <v>29500</v>
+      </c>
+      <c r="L71" t="n">
+        <v>24300</v>
+      </c>
+      <c r="M71" t="n">
+        <v>38000</v>
+      </c>
+      <c r="N71" t="n">
+        <v>24900</v>
+      </c>
+      <c r="O71" t="n">
+        <v>27450</v>
+      </c>
+      <c r="P71" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>195</v>
+      </c>
+      <c r="R71" t="n">
+        <v>201</v>
+      </c>
+      <c r="S71" t="n">
+        <v>50</v>
+      </c>
+      <c r="T71" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="72">
@@ -2235,7 +4922,7 @@
         <v>11</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E72" t="n">
         <v>29000</v>
@@ -2244,7 +4931,46 @@
         <v>250</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K72" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L72" t="n">
+        <v>20900</v>
+      </c>
+      <c r="M72" t="n">
+        <v>31200</v>
+      </c>
+      <c r="N72" t="n">
+        <v>28466.66666666667</v>
+      </c>
+      <c r="O72" t="n">
+        <v>26950</v>
+      </c>
+      <c r="P72" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>175</v>
+      </c>
+      <c r="R72" t="n">
+        <v>230.3333333333333</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-33</v>
+      </c>
+      <c r="T72" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="73">
@@ -2260,7 +4986,7 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E73" t="n">
         <v>28300</v>
@@ -2269,7 +4995,46 @@
         <v>235</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L73" t="n">
+        <v>29500</v>
+      </c>
+      <c r="M73" t="n">
+        <v>20800</v>
+      </c>
+      <c r="N73" t="n">
+        <v>31166.66666666667</v>
+      </c>
+      <c r="O73" t="n">
+        <v>26583.33333333333</v>
+      </c>
+      <c r="P73" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>233</v>
+      </c>
+      <c r="R73" t="n">
+        <v>255.3333333333333</v>
+      </c>
+      <c r="S73" t="n">
+        <v>-15</v>
+      </c>
+      <c r="T73" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -2285,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E74" t="n">
         <v>37165</v>
@@ -2294,7 +5059,28 @@
         <v>61</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2310,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E75" t="n">
         <v>49722</v>
@@ -2319,7 +5105,34 @@
         <v>78</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K75" t="n">
+        <v>37165</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>17</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2335,7 +5148,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E76" t="n">
         <v>57135</v>
@@ -2344,7 +5157,34 @@
         <v>85</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K76" t="n">
+        <v>49722</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>7</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2360,7 +5200,7 @@
         <v>4</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E77" t="n">
         <v>38372</v>
@@ -2369,7 +5209,42 @@
         <v>58</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K77" t="n">
+        <v>57135</v>
+      </c>
+      <c r="L77" t="n">
+        <v>37165</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>48007.33333333334</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>61</v>
+      </c>
+      <c r="R77" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="S77" t="n">
+        <v>-27</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2385,7 +5260,7 @@
         <v>5</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E78" t="n">
         <v>49984</v>
@@ -2394,7 +5269,42 @@
         <v>75</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K78" t="n">
+        <v>38372</v>
+      </c>
+      <c r="L78" t="n">
+        <v>49722</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>48409.66666666666</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>78</v>
+      </c>
+      <c r="R78" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="S78" t="n">
+        <v>17</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -2410,7 +5320,7 @@
         <v>6</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E79" t="n">
         <v>37888</v>
@@ -2419,7 +5329,42 @@
         <v>57</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>49984</v>
+      </c>
+      <c r="L79" t="n">
+        <v>57135</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>48497</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>85</v>
+      </c>
+      <c r="R79" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="S79" t="n">
+        <v>-18</v>
+      </c>
+      <c r="T79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -2435,7 +5380,7 @@
         <v>7</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E80" t="n">
         <v>40745</v>
@@ -2444,7 +5389,46 @@
         <v>59</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K80" t="n">
+        <v>37888</v>
+      </c>
+      <c r="L80" t="n">
+        <v>38372</v>
+      </c>
+      <c r="M80" t="n">
+        <v>37165</v>
+      </c>
+      <c r="N80" t="n">
+        <v>42081.33333333334</v>
+      </c>
+      <c r="O80" t="n">
+        <v>45044.33333333334</v>
+      </c>
+      <c r="P80" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>58</v>
+      </c>
+      <c r="R80" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -2460,7 +5444,7 @@
         <v>8</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E81" t="n">
         <v>95171</v>
@@ -2469,7 +5453,46 @@
         <v>167</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K81" t="n">
+        <v>40745</v>
+      </c>
+      <c r="L81" t="n">
+        <v>49984</v>
+      </c>
+      <c r="M81" t="n">
+        <v>49722</v>
+      </c>
+      <c r="N81" t="n">
+        <v>42872.33333333334</v>
+      </c>
+      <c r="O81" t="n">
+        <v>45641</v>
+      </c>
+      <c r="P81" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>75</v>
+      </c>
+      <c r="R81" t="n">
+        <v>63.66666666666666</v>
+      </c>
+      <c r="S81" t="n">
+        <v>108</v>
+      </c>
+      <c r="T81" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2485,7 +5508,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E82" t="n">
         <v>44703</v>
@@ -2494,7 +5517,46 @@
         <v>64</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K82" t="n">
+        <v>95171</v>
+      </c>
+      <c r="L82" t="n">
+        <v>37888</v>
+      </c>
+      <c r="M82" t="n">
+        <v>57135</v>
+      </c>
+      <c r="N82" t="n">
+        <v>57934.66666666666</v>
+      </c>
+      <c r="O82" t="n">
+        <v>53215.83333333334</v>
+      </c>
+      <c r="P82" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>57</v>
+      </c>
+      <c r="R82" t="n">
+        <v>94.33333333333333</v>
+      </c>
+      <c r="S82" t="n">
+        <v>-103</v>
+      </c>
+      <c r="T82" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2510,7 +5572,7 @@
         <v>10</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E83" t="n">
         <v>47834</v>
@@ -2519,7 +5581,46 @@
         <v>74</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K83" t="n">
+        <v>44703</v>
+      </c>
+      <c r="L83" t="n">
+        <v>40745</v>
+      </c>
+      <c r="M83" t="n">
+        <v>38372</v>
+      </c>
+      <c r="N83" t="n">
+        <v>60206.33333333334</v>
+      </c>
+      <c r="O83" t="n">
+        <v>51143.83333333334</v>
+      </c>
+      <c r="P83" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>59</v>
+      </c>
+      <c r="R83" t="n">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -2535,7 +5636,7 @@
         <v>11</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E84" t="n">
         <v>46258</v>
@@ -2544,7 +5645,46 @@
         <v>60</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K84" t="n">
+        <v>47834</v>
+      </c>
+      <c r="L84" t="n">
+        <v>95171</v>
+      </c>
+      <c r="M84" t="n">
+        <v>49984</v>
+      </c>
+      <c r="N84" t="n">
+        <v>62569.33333333334</v>
+      </c>
+      <c r="O84" t="n">
+        <v>52720.83333333334</v>
+      </c>
+      <c r="P84" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>167</v>
+      </c>
+      <c r="R84" t="n">
+        <v>101.6666666666667</v>
+      </c>
+      <c r="S84" t="n">
+        <v>-14</v>
+      </c>
+      <c r="T84" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -2560,7 +5700,7 @@
         <v>12</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E85" t="n">
         <v>41697</v>
@@ -2569,7 +5709,46 @@
         <v>67</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L85" t="n">
+        <v>44703</v>
+      </c>
+      <c r="M85" t="n">
+        <v>37888</v>
+      </c>
+      <c r="N85" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O85" t="n">
+        <v>52099.83333333334</v>
+      </c>
+      <c r="P85" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>64</v>
+      </c>
+      <c r="R85" t="n">
+        <v>66</v>
+      </c>
+      <c r="S85" t="n">
+        <v>7</v>
+      </c>
+      <c r="T85" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="86">
@@ -2585,7 +5764,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E86" t="n">
         <v>37534</v>
@@ -2594,7 +5773,46 @@
         <v>48</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K86" t="n">
+        <v>41697</v>
+      </c>
+      <c r="L86" t="n">
+        <v>47834</v>
+      </c>
+      <c r="M86" t="n">
+        <v>40745</v>
+      </c>
+      <c r="N86" t="n">
+        <v>45263</v>
+      </c>
+      <c r="O86" t="n">
+        <v>52734.66666666666</v>
+      </c>
+      <c r="P86" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>74</v>
+      </c>
+      <c r="R86" t="n">
+        <v>67</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-19</v>
+      </c>
+      <c r="T86" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -2610,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E87" t="n">
         <v>44304</v>
@@ -2619,7 +5837,46 @@
         <v>62</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K87" t="n">
+        <v>37534</v>
+      </c>
+      <c r="L87" t="n">
+        <v>46258</v>
+      </c>
+      <c r="M87" t="n">
+        <v>95171</v>
+      </c>
+      <c r="N87" t="n">
+        <v>41829.66666666666</v>
+      </c>
+      <c r="O87" t="n">
+        <v>52199.5</v>
+      </c>
+      <c r="P87" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>60</v>
+      </c>
+      <c r="R87" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="S87" t="n">
+        <v>14</v>
+      </c>
+      <c r="T87" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="88">
@@ -2635,7 +5892,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E88" t="n">
         <v>29894</v>
@@ -2644,7 +5901,46 @@
         <v>48</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K88" t="n">
+        <v>44304</v>
+      </c>
+      <c r="L88" t="n">
+        <v>41697</v>
+      </c>
+      <c r="M88" t="n">
+        <v>44703</v>
+      </c>
+      <c r="N88" t="n">
+        <v>41178.33333333334</v>
+      </c>
+      <c r="O88" t="n">
+        <v>43721.66666666666</v>
+      </c>
+      <c r="P88" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>67</v>
+      </c>
+      <c r="R88" t="n">
+        <v>59</v>
+      </c>
+      <c r="S88" t="n">
+        <v>-14</v>
+      </c>
+      <c r="T88" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="89">
@@ -2660,7 +5956,7 @@
         <v>4</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E89" t="n">
         <v>69986</v>
@@ -2669,7 +5965,46 @@
         <v>119</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K89" t="n">
+        <v>29894</v>
+      </c>
+      <c r="L89" t="n">
+        <v>37534</v>
+      </c>
+      <c r="M89" t="n">
+        <v>47834</v>
+      </c>
+      <c r="N89" t="n">
+        <v>37244</v>
+      </c>
+      <c r="O89" t="n">
+        <v>41253.5</v>
+      </c>
+      <c r="P89" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>48</v>
+      </c>
+      <c r="R89" t="n">
+        <v>52.66666666666666</v>
+      </c>
+      <c r="S89" t="n">
+        <v>71</v>
+      </c>
+      <c r="T89" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="90">
@@ -2685,7 +6020,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E90" t="n">
         <v>57097</v>
@@ -2694,7 +6029,46 @@
         <v>85</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K90" t="n">
+        <v>69986</v>
+      </c>
+      <c r="L90" t="n">
+        <v>44304</v>
+      </c>
+      <c r="M90" t="n">
+        <v>46258</v>
+      </c>
+      <c r="N90" t="n">
+        <v>48061.33333333334</v>
+      </c>
+      <c r="O90" t="n">
+        <v>44945.5</v>
+      </c>
+      <c r="P90" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>62</v>
+      </c>
+      <c r="R90" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="S90" t="n">
+        <v>-34</v>
+      </c>
+      <c r="T90" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="91">
@@ -2710,7 +6084,7 @@
         <v>6</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E91" t="n">
         <v>253987</v>
@@ -2719,7 +6093,46 @@
         <v>301</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>57097</v>
+      </c>
+      <c r="L91" t="n">
+        <v>29894</v>
+      </c>
+      <c r="M91" t="n">
+        <v>41697</v>
+      </c>
+      <c r="N91" t="n">
+        <v>52325.66666666666</v>
+      </c>
+      <c r="O91" t="n">
+        <v>46752</v>
+      </c>
+      <c r="P91" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>48</v>
+      </c>
+      <c r="R91" t="n">
+        <v>84</v>
+      </c>
+      <c r="S91" t="n">
+        <v>216</v>
+      </c>
+      <c r="T91" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="92">
@@ -2735,7 +6148,7 @@
         <v>7</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E92" t="n">
         <v>63935</v>
@@ -2744,7 +6157,46 @@
         <v>91</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K92" t="n">
+        <v>253987</v>
+      </c>
+      <c r="L92" t="n">
+        <v>69986</v>
+      </c>
+      <c r="M92" t="n">
+        <v>37534</v>
+      </c>
+      <c r="N92" t="n">
+        <v>127023.3333333333</v>
+      </c>
+      <c r="O92" t="n">
+        <v>82133.66666666667</v>
+      </c>
+      <c r="P92" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>119</v>
+      </c>
+      <c r="R92" t="n">
+        <v>168.3333333333333</v>
+      </c>
+      <c r="S92" t="n">
+        <v>-210</v>
+      </c>
+      <c r="T92" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -2760,7 +6212,7 @@
         <v>8</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E93" t="n">
         <v>63208</v>
@@ -2769,7 +6221,46 @@
         <v>99</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J93" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K93" t="n">
+        <v>63935</v>
+      </c>
+      <c r="L93" t="n">
+        <v>57097</v>
+      </c>
+      <c r="M93" t="n">
+        <v>44304</v>
+      </c>
+      <c r="N93" t="n">
+        <v>125006.3333333333</v>
+      </c>
+      <c r="O93" t="n">
+        <v>86533.83333333333</v>
+      </c>
+      <c r="P93" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>85</v>
+      </c>
+      <c r="R93" t="n">
+        <v>159</v>
+      </c>
+      <c r="S93" t="n">
+        <v>8</v>
+      </c>
+      <c r="T93" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -2785,7 +6276,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E94" t="n">
         <v>50886</v>
@@ -2794,7 +6285,46 @@
         <v>72</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K94" t="n">
+        <v>63208</v>
+      </c>
+      <c r="L94" t="n">
+        <v>253987</v>
+      </c>
+      <c r="M94" t="n">
+        <v>29894</v>
+      </c>
+      <c r="N94" t="n">
+        <v>127043.3333333333</v>
+      </c>
+      <c r="O94" t="n">
+        <v>89684.5</v>
+      </c>
+      <c r="P94" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>301</v>
+      </c>
+      <c r="R94" t="n">
+        <v>163.6666666666667</v>
+      </c>
+      <c r="S94" t="n">
+        <v>-27</v>
+      </c>
+      <c r="T94" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="95">
@@ -2810,7 +6340,7 @@
         <v>10</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E95" t="n">
         <v>74755</v>
@@ -2819,7 +6349,46 @@
         <v>115</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K95" t="n">
+        <v>50886</v>
+      </c>
+      <c r="L95" t="n">
+        <v>63935</v>
+      </c>
+      <c r="M95" t="n">
+        <v>69986</v>
+      </c>
+      <c r="N95" t="n">
+        <v>59343</v>
+      </c>
+      <c r="O95" t="n">
+        <v>93183.16666666667</v>
+      </c>
+      <c r="P95" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>91</v>
+      </c>
+      <c r="R95" t="n">
+        <v>87.33333333333333</v>
+      </c>
+      <c r="S95" t="n">
+        <v>43</v>
+      </c>
+      <c r="T95" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="96">
@@ -2835,7 +6404,7 @@
         <v>11</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E96" t="n">
         <v>65216</v>
@@ -2844,7 +6413,46 @@
         <v>99</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K96" t="n">
+        <v>74755</v>
+      </c>
+      <c r="L96" t="n">
+        <v>63208</v>
+      </c>
+      <c r="M96" t="n">
+        <v>57097</v>
+      </c>
+      <c r="N96" t="n">
+        <v>62949.66666666666</v>
+      </c>
+      <c r="O96" t="n">
+        <v>93978</v>
+      </c>
+      <c r="P96" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>99</v>
+      </c>
+      <c r="R96" t="n">
+        <v>95.33333333333333</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T96" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -2860,7 +6468,7 @@
         <v>12</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E97" t="n">
         <v>67406</v>
@@ -2869,7 +6477,46 @@
         <v>88</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>65216</v>
+      </c>
+      <c r="L97" t="n">
+        <v>50886</v>
+      </c>
+      <c r="M97" t="n">
+        <v>253987</v>
+      </c>
+      <c r="N97" t="n">
+        <v>63619</v>
+      </c>
+      <c r="O97" t="n">
+        <v>95331.16666666667</v>
+      </c>
+      <c r="P97" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>72</v>
+      </c>
+      <c r="R97" t="n">
+        <v>95.33333333333333</v>
+      </c>
+      <c r="S97" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T97" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="98">
@@ -2885,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E98" t="n">
         <v>42291</v>
@@ -2894,7 +6541,46 @@
         <v>59</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K98" t="n">
+        <v>67406</v>
+      </c>
+      <c r="L98" t="n">
+        <v>74755</v>
+      </c>
+      <c r="M98" t="n">
+        <v>63935</v>
+      </c>
+      <c r="N98" t="n">
+        <v>69125.66666666667</v>
+      </c>
+      <c r="O98" t="n">
+        <v>64234.33333333334</v>
+      </c>
+      <c r="P98" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>115</v>
+      </c>
+      <c r="R98" t="n">
+        <v>100.6666666666667</v>
+      </c>
+      <c r="S98" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T98" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="99">
@@ -2910,7 +6596,7 @@
         <v>2</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E99" t="n">
         <v>42880</v>
@@ -2919,7 +6605,46 @@
         <v>56</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K99" t="n">
+        <v>42291</v>
+      </c>
+      <c r="L99" t="n">
+        <v>65216</v>
+      </c>
+      <c r="M99" t="n">
+        <v>63208</v>
+      </c>
+      <c r="N99" t="n">
+        <v>58304.33333333334</v>
+      </c>
+      <c r="O99" t="n">
+        <v>60627</v>
+      </c>
+      <c r="P99" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>99</v>
+      </c>
+      <c r="R99" t="n">
+        <v>82</v>
+      </c>
+      <c r="S99" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T99" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="100">
@@ -2935,7 +6660,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E100" t="n">
         <v>55776</v>
@@ -2944,7 +6669,46 @@
         <v>79</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K100" t="n">
+        <v>42880</v>
+      </c>
+      <c r="L100" t="n">
+        <v>67406</v>
+      </c>
+      <c r="M100" t="n">
+        <v>50886</v>
+      </c>
+      <c r="N100" t="n">
+        <v>50859</v>
+      </c>
+      <c r="O100" t="n">
+        <v>57239</v>
+      </c>
+      <c r="P100" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>88</v>
+      </c>
+      <c r="R100" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="S100" t="n">
+        <v>23</v>
+      </c>
+      <c r="T100" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="101">
@@ -2960,7 +6724,7 @@
         <v>4</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E101" t="n">
         <v>51315</v>
@@ -2969,7 +6733,46 @@
         <v>68</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K101" t="n">
+        <v>55776</v>
+      </c>
+      <c r="L101" t="n">
+        <v>42291</v>
+      </c>
+      <c r="M101" t="n">
+        <v>74755</v>
+      </c>
+      <c r="N101" t="n">
+        <v>46982.33333333334</v>
+      </c>
+      <c r="O101" t="n">
+        <v>58054</v>
+      </c>
+      <c r="P101" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>59</v>
+      </c>
+      <c r="R101" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T101" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="102">
@@ -2985,7 +6788,7 @@
         <v>5</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E102" t="n">
         <v>53420</v>
@@ -2994,7 +6797,46 @@
         <v>72</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J102" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K102" t="n">
+        <v>51315</v>
+      </c>
+      <c r="L102" t="n">
+        <v>42880</v>
+      </c>
+      <c r="M102" t="n">
+        <v>65216</v>
+      </c>
+      <c r="N102" t="n">
+        <v>49990.33333333334</v>
+      </c>
+      <c r="O102" t="n">
+        <v>54147.33333333334</v>
+      </c>
+      <c r="P102" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>56</v>
+      </c>
+      <c r="R102" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="S102" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="103">
@@ -3010,7 +6852,7 @@
         <v>6</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E103" t="n">
         <v>41967</v>
@@ -3019,7 +6861,46 @@
         <v>59</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>53420</v>
+      </c>
+      <c r="L103" t="n">
+        <v>55776</v>
+      </c>
+      <c r="M103" t="n">
+        <v>67406</v>
+      </c>
+      <c r="N103" t="n">
+        <v>53503.66666666666</v>
+      </c>
+      <c r="O103" t="n">
+        <v>52181.33333333334</v>
+      </c>
+      <c r="P103" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>79</v>
+      </c>
+      <c r="R103" t="n">
+        <v>73</v>
+      </c>
+      <c r="S103" t="n">
+        <v>-13</v>
+      </c>
+      <c r="T103" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="104">
@@ -3035,7 +6916,7 @@
         <v>7</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E104" t="n">
         <v>46371</v>
@@ -3044,7 +6925,46 @@
         <v>59</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K104" t="n">
+        <v>41967</v>
+      </c>
+      <c r="L104" t="n">
+        <v>51315</v>
+      </c>
+      <c r="M104" t="n">
+        <v>42291</v>
+      </c>
+      <c r="N104" t="n">
+        <v>48900.66666666666</v>
+      </c>
+      <c r="O104" t="n">
+        <v>47941.5</v>
+      </c>
+      <c r="P104" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>68</v>
+      </c>
+      <c r="R104" t="n">
+        <v>66.33333333333333</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="105">
@@ -3060,7 +6980,7 @@
         <v>8</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E105" t="n">
         <v>36850</v>
@@ -3069,7 +6989,46 @@
         <v>51</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J105" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K105" t="n">
+        <v>46371</v>
+      </c>
+      <c r="L105" t="n">
+        <v>53420</v>
+      </c>
+      <c r="M105" t="n">
+        <v>42880</v>
+      </c>
+      <c r="N105" t="n">
+        <v>47252.66666666666</v>
+      </c>
+      <c r="O105" t="n">
+        <v>48621.5</v>
+      </c>
+      <c r="P105" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>72</v>
+      </c>
+      <c r="R105" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="S105" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T105" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="106">
@@ -3085,7 +7044,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E106" t="n">
         <v>40080</v>
@@ -3094,7 +7053,46 @@
         <v>61</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K106" t="n">
+        <v>36850</v>
+      </c>
+      <c r="L106" t="n">
+        <v>41967</v>
+      </c>
+      <c r="M106" t="n">
+        <v>55776</v>
+      </c>
+      <c r="N106" t="n">
+        <v>41729.33333333334</v>
+      </c>
+      <c r="O106" t="n">
+        <v>47616.5</v>
+      </c>
+      <c r="P106" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>59</v>
+      </c>
+      <c r="R106" t="n">
+        <v>56.33333333333334</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="107">
@@ -3110,7 +7108,7 @@
         <v>10</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E107" t="n">
         <v>65171</v>
@@ -3119,7 +7117,46 @@
         <v>73</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H107" t="n">
+        <v>4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K107" t="n">
+        <v>40080</v>
+      </c>
+      <c r="L107" t="n">
+        <v>46371</v>
+      </c>
+      <c r="M107" t="n">
+        <v>51315</v>
+      </c>
+      <c r="N107" t="n">
+        <v>41100.33333333334</v>
+      </c>
+      <c r="O107" t="n">
+        <v>45000.5</v>
+      </c>
+      <c r="P107" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>59</v>
+      </c>
+      <c r="R107" t="n">
+        <v>57</v>
+      </c>
+      <c r="S107" t="n">
+        <v>12</v>
+      </c>
+      <c r="T107" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="108">
@@ -3135,7 +7172,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E108" t="n">
         <v>37311</v>
@@ -3144,7 +7181,46 @@
         <v>57</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H108" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K108" t="n">
+        <v>65171</v>
+      </c>
+      <c r="L108" t="n">
+        <v>36850</v>
+      </c>
+      <c r="M108" t="n">
+        <v>53420</v>
+      </c>
+      <c r="N108" t="n">
+        <v>47367</v>
+      </c>
+      <c r="O108" t="n">
+        <v>47309.83333333334</v>
+      </c>
+      <c r="P108" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>51</v>
+      </c>
+      <c r="R108" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="S108" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T108" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="109">
@@ -3160,7 +7236,7 @@
         <v>12</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E109" t="n">
         <v>54438</v>
@@ -3169,7 +7245,46 @@
         <v>78</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H109" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>37311</v>
+      </c>
+      <c r="L109" t="n">
+        <v>40080</v>
+      </c>
+      <c r="M109" t="n">
+        <v>41967</v>
+      </c>
+      <c r="N109" t="n">
+        <v>47520.66666666666</v>
+      </c>
+      <c r="O109" t="n">
+        <v>44625</v>
+      </c>
+      <c r="P109" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>61</v>
+      </c>
+      <c r="R109" t="n">
+        <v>63.66666666666666</v>
+      </c>
+      <c r="S109" t="n">
+        <v>21</v>
+      </c>
+      <c r="T109" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="110">
@@ -3185,7 +7300,7 @@
         <v>5</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E110" t="n">
         <v>3000</v>
@@ -3194,7 +7309,28 @@
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3210,7 +7346,7 @@
         <v>6</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E111" t="n">
         <v>3000</v>
@@ -3219,7 +7355,34 @@
         <v>1</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3235,7 +7398,7 @@
         <v>10</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E112" t="n">
         <v>3000</v>
@@ -3244,7 +7407,34 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3260,7 +7450,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E113" t="n">
         <v>2000</v>
@@ -3269,7 +7459,42 @@
         <v>2</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L113" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1</v>
+      </c>
+      <c r="R113" t="n">
+        <v>1</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3285,7 +7510,7 @@
         <v>4</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E114" t="n">
         <v>10000</v>
@@ -3294,7 +7519,42 @@
         <v>3</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J114" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L114" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -3310,7 +7570,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E115" t="n">
         <v>3000</v>
@@ -3319,7 +7579,42 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J115" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K115" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L115" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T115" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -3335,7 +7630,7 @@
         <v>6</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E116" t="n">
         <v>1000</v>
@@ -3344,7 +7639,46 @@
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N116" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O116" t="n">
+        <v>4000</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>2</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -3360,7 +7694,7 @@
         <v>7</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E117" t="n">
         <v>1000</v>
@@ -3369,7 +7703,46 @@
         <v>1</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L117" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M117" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N117" t="n">
+        <v>4666.666666666667</v>
+      </c>
+      <c r="O117" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>3</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="118">
@@ -3385,7 +7758,7 @@
         <v>8</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E118" t="n">
         <v>2000</v>
@@ -3394,7 +7767,46 @@
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L118" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1666.666666666667</v>
+      </c>
+      <c r="O118" t="n">
+        <v>3333.333333333333</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -3410,7 +7822,7 @@
         <v>10</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E119" t="n">
         <v>6000</v>
@@ -3419,7 +7831,46 @@
         <v>3</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1333.333333333333</v>
+      </c>
+      <c r="O119" t="n">
+        <v>3166.666666666667</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>2</v>
+      </c>
+      <c r="T119" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="120">
@@ -3435,7 +7886,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E120" t="n">
         <v>8000</v>
@@ -3444,7 +7895,46 @@
         <v>4</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K120" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N120" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O120" t="n">
+        <v>3833.333333333333</v>
+      </c>
+      <c r="P120" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="121">
@@ -3460,7 +7950,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E121" t="n">
         <v>5000</v>
@@ -3469,7 +7959,46 @@
         <v>3</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K121" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N121" t="n">
+        <v>5333.333333333333</v>
+      </c>
+      <c r="O121" t="n">
+        <v>3500</v>
+      </c>
+      <c r="P121" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1</v>
+      </c>
+      <c r="R121" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T121" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="122">
@@ -3485,7 +8014,7 @@
         <v>5</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E122" t="n">
         <v>6000</v>
@@ -3494,7 +8023,46 @@
         <v>4</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L122" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N122" t="n">
+        <v>6333.333333333333</v>
+      </c>
+      <c r="O122" t="n">
+        <v>3833.333333333333</v>
+      </c>
+      <c r="P122" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>3</v>
+      </c>
+      <c r="R122" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="123">
@@ -3510,7 +8078,7 @@
         <v>6</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E123" t="n">
         <v>4000</v>
@@ -3519,7 +8087,46 @@
         <v>3</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L123" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N123" t="n">
+        <v>6333.333333333333</v>
+      </c>
+      <c r="O123" t="n">
+        <v>4666.666666666667</v>
+      </c>
+      <c r="P123" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>4</v>
+      </c>
+      <c r="R123" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="S123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T123" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="124">
@@ -3535,7 +8142,7 @@
         <v>7</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E124" t="n">
         <v>1000</v>
@@ -3544,7 +8151,46 @@
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K124" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L124" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M124" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N124" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O124" t="n">
+        <v>5166.666666666667</v>
+      </c>
+      <c r="P124" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>3</v>
+      </c>
+      <c r="R124" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S124" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T124" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="125">
@@ -3560,7 +8206,7 @@
         <v>8</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E125" t="n">
         <v>2000</v>
@@ -3569,7 +8215,46 @@
         <v>2</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="O125" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>4</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="T125" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="126">
@@ -3585,7 +8270,7 @@
         <v>9</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E126" t="n">
         <v>2000</v>
@@ -3594,7 +8279,46 @@
         <v>2</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L126" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M126" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="O126" t="n">
+        <v>4333.333333333333</v>
+      </c>
+      <c r="P126" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>3</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="127">
@@ -3610,7 +8334,7 @@
         <v>10</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E127" t="n">
         <v>3000</v>
@@ -3619,7 +8343,46 @@
         <v>2</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M127" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1666.666666666667</v>
+      </c>
+      <c r="O127" t="n">
+        <v>3333.333333333333</v>
+      </c>
+      <c r="P127" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="128">
@@ -3635,7 +8398,7 @@
         <v>11</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E128" t="n">
         <v>3000</v>
@@ -3644,7 +8407,46 @@
         <v>3</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M128" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N128" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="O128" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P128" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>2</v>
+      </c>
+      <c r="R128" t="n">
+        <v>2</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="129">
@@ -3660,7 +8462,7 @@
         <v>12</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E129" t="n">
         <v>3000</v>
@@ -3669,7 +8471,46 @@
         <v>2</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L129" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M129" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N129" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="O129" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P129" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>2</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="S129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T129" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="130">
@@ -3685,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E130" t="n">
         <v>3800</v>
@@ -3694,7 +8535,28 @@
         <v>38</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -3710,7 +8572,7 @@
         <v>2</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E131" t="n">
         <v>4500</v>
@@ -3719,7 +8581,34 @@
         <v>45</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K131" t="n">
+        <v>3800</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="n">
+        <v>7</v>
+      </c>
+      <c r="T131" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3735,7 +8624,7 @@
         <v>3</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E132" t="n">
         <v>3600</v>
@@ -3744,7 +8633,34 @@
         <v>36</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K132" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T132" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3760,7 +8676,7 @@
         <v>4</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E133" t="n">
         <v>2500</v>
@@ -3769,7 +8685,42 @@
         <v>25</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K133" t="n">
+        <v>3600</v>
+      </c>
+      <c r="L133" t="n">
+        <v>3800</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>3966.666666666667</v>
+      </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>38</v>
+      </c>
+      <c r="R133" t="n">
+        <v>39.66666666666666</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T133" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3785,7 +8736,7 @@
         <v>5</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E134" t="n">
         <v>2600</v>
@@ -3794,7 +8745,42 @@
         <v>26</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K134" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L134" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>3533.333333333333</v>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>45</v>
+      </c>
+      <c r="R134" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="135">
@@ -3810,7 +8796,7 @@
         <v>6</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E135" t="n">
         <v>1100</v>
@@ -3819,7 +8805,42 @@
         <v>11</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2600</v>
+      </c>
+      <c r="L135" t="n">
+        <v>3600</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>2900</v>
+      </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>36</v>
+      </c>
+      <c r="R135" t="n">
+        <v>29</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-15</v>
+      </c>
+      <c r="T135" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -3835,7 +8856,7 @@
         <v>7</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E136" t="n">
         <v>2100</v>
@@ -3844,7 +8865,46 @@
         <v>21</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L136" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M136" t="n">
+        <v>3800</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2066.666666666667</v>
+      </c>
+      <c r="O136" t="n">
+        <v>3016.666666666667</v>
+      </c>
+      <c r="P136" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>25</v>
+      </c>
+      <c r="R136" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="137">
@@ -3860,7 +8920,7 @@
         <v>8</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E137" t="n">
         <v>7600</v>
@@ -3869,7 +8929,46 @@
         <v>76</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2100</v>
+      </c>
+      <c r="L137" t="n">
+        <v>2600</v>
+      </c>
+      <c r="M137" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1933.333333333333</v>
+      </c>
+      <c r="O137" t="n">
+        <v>2733.333333333333</v>
+      </c>
+      <c r="P137" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>26</v>
+      </c>
+      <c r="R137" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="S137" t="n">
+        <v>55</v>
+      </c>
+      <c r="T137" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -3885,7 +8984,7 @@
         <v>9</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E138" t="n">
         <v>2800</v>
@@ -3894,7 +8993,46 @@
         <v>28</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K138" t="n">
+        <v>7600</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M138" t="n">
+        <v>3600</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3600</v>
+      </c>
+      <c r="O138" t="n">
+        <v>3250</v>
+      </c>
+      <c r="P138" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>11</v>
+      </c>
+      <c r="R138" t="n">
+        <v>36</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-48</v>
+      </c>
+      <c r="T138" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -3910,7 +9048,7 @@
         <v>10</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E139" t="n">
         <v>5000</v>
@@ -3919,7 +9057,46 @@
         <v>50</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2800</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M139" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4166.666666666667</v>
+      </c>
+      <c r="O139" t="n">
+        <v>3116.666666666667</v>
+      </c>
+      <c r="P139" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>21</v>
+      </c>
+      <c r="R139" t="n">
+        <v>41.66666666666666</v>
+      </c>
+      <c r="S139" t="n">
+        <v>22</v>
+      </c>
+      <c r="T139" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="140">
@@ -3935,7 +9112,7 @@
         <v>11</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E140" t="n">
         <v>1600</v>
@@ -3944,7 +9121,46 @@
         <v>16</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H140" t="n">
+        <v>4</v>
+      </c>
+      <c r="I140" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7600</v>
+      </c>
+      <c r="M140" t="n">
+        <v>2600</v>
+      </c>
+      <c r="N140" t="n">
+        <v>5133.333333333333</v>
+      </c>
+      <c r="O140" t="n">
+        <v>3533.333333333333</v>
+      </c>
+      <c r="P140" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>76</v>
+      </c>
+      <c r="R140" t="n">
+        <v>51.33333333333334</v>
+      </c>
+      <c r="S140" t="n">
+        <v>-34</v>
+      </c>
+      <c r="T140" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="141">
@@ -3960,7 +9176,7 @@
         <v>12</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E141" t="n">
         <v>2800</v>
@@ -3969,7 +9185,46 @@
         <v>28</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L141" t="n">
+        <v>2800</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1100</v>
+      </c>
+      <c r="N141" t="n">
+        <v>3133.333333333333</v>
+      </c>
+      <c r="O141" t="n">
+        <v>3366.666666666667</v>
+      </c>
+      <c r="P141" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>28</v>
+      </c>
+      <c r="R141" t="n">
+        <v>31.33333333333333</v>
+      </c>
+      <c r="S141" t="n">
+        <v>12</v>
+      </c>
+      <c r="T141" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="142">
@@ -3985,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E142" t="n">
         <v>1900</v>
@@ -3994,7 +9249,46 @@
         <v>19</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2800</v>
+      </c>
+      <c r="L142" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M142" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3133.333333333333</v>
+      </c>
+      <c r="O142" t="n">
+        <v>3650</v>
+      </c>
+      <c r="P142" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>50</v>
+      </c>
+      <c r="R142" t="n">
+        <v>31.33333333333333</v>
+      </c>
+      <c r="S142" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T142" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="143">
@@ -4010,7 +9304,7 @@
         <v>2</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E143" t="n">
         <v>1800</v>
@@ -4019,7 +9313,46 @@
         <v>18</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1900</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1600</v>
+      </c>
+      <c r="M143" t="n">
+        <v>7600</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2100</v>
+      </c>
+      <c r="O143" t="n">
+        <v>3616.666666666667</v>
+      </c>
+      <c r="P143" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>16</v>
+      </c>
+      <c r="R143" t="n">
+        <v>21</v>
+      </c>
+      <c r="S143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T143" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="144">
@@ -4035,7 +9368,7 @@
         <v>3</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E144" t="n">
         <v>9700</v>
@@ -4044,7 +9377,46 @@
         <v>97</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L144" t="n">
+        <v>2800</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2800</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2166.666666666667</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2650</v>
+      </c>
+      <c r="P144" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>28</v>
+      </c>
+      <c r="R144" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="S144" t="n">
+        <v>79</v>
+      </c>
+      <c r="T144" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="145">
@@ -4060,7 +9432,7 @@
         <v>4</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E145" t="n">
         <v>5200</v>
@@ -4069,7 +9441,46 @@
         <v>52</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K145" t="n">
+        <v>9700</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M145" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N145" t="n">
+        <v>4466.666666666667</v>
+      </c>
+      <c r="O145" t="n">
+        <v>3800</v>
+      </c>
+      <c r="P145" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>19</v>
+      </c>
+      <c r="R145" t="n">
+        <v>44.66666666666666</v>
+      </c>
+      <c r="S145" t="n">
+        <v>-45</v>
+      </c>
+      <c r="T145" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="146">
@@ -4085,7 +9496,7 @@
         <v>5</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E146" t="n">
         <v>2300</v>
@@ -4094,7 +9505,46 @@
         <v>23</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J146" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K146" t="n">
+        <v>5200</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N146" t="n">
+        <v>5566.666666666667</v>
+      </c>
+      <c r="O146" t="n">
+        <v>3833.333333333333</v>
+      </c>
+      <c r="P146" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>18</v>
+      </c>
+      <c r="R146" t="n">
+        <v>55.66666666666666</v>
+      </c>
+      <c r="S146" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T146" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="147">
@@ -4110,7 +9560,7 @@
         <v>6</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E147" t="n">
         <v>1300</v>
@@ -4119,7 +9569,46 @@
         <v>13</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L147" t="n">
+        <v>9700</v>
+      </c>
+      <c r="M147" t="n">
+        <v>2800</v>
+      </c>
+      <c r="N147" t="n">
+        <v>5733.333333333333</v>
+      </c>
+      <c r="O147" t="n">
+        <v>3950</v>
+      </c>
+      <c r="P147" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>97</v>
+      </c>
+      <c r="R147" t="n">
+        <v>57.33333333333334</v>
+      </c>
+      <c r="S147" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T147" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="148">
@@ -4135,7 +9624,7 @@
         <v>7</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E148" t="n">
         <v>7300</v>
@@ -4144,7 +9633,46 @@
         <v>73</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J148" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L148" t="n">
+        <v>5200</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N148" t="n">
+        <v>2933.333333333333</v>
+      </c>
+      <c r="O148" t="n">
+        <v>3700</v>
+      </c>
+      <c r="P148" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>52</v>
+      </c>
+      <c r="R148" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="S148" t="n">
+        <v>60</v>
+      </c>
+      <c r="T148" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="149">
@@ -4160,7 +9688,7 @@
         <v>8</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E149" t="n">
         <v>9200</v>
@@ -4169,7 +9697,46 @@
         <v>92</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J149" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K149" t="n">
+        <v>7300</v>
+      </c>
+      <c r="L149" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N149" t="n">
+        <v>3633.333333333333</v>
+      </c>
+      <c r="O149" t="n">
+        <v>4600</v>
+      </c>
+      <c r="P149" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>23</v>
+      </c>
+      <c r="R149" t="n">
+        <v>36.33333333333334</v>
+      </c>
+      <c r="S149" t="n">
+        <v>19</v>
+      </c>
+      <c r="T149" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="150">
@@ -4185,7 +9752,7 @@
         <v>9</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E150" t="n">
         <v>2400</v>
@@ -4194,7 +9761,46 @@
         <v>24</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K150" t="n">
+        <v>9200</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M150" t="n">
+        <v>9700</v>
+      </c>
+      <c r="N150" t="n">
+        <v>5933.333333333333</v>
+      </c>
+      <c r="O150" t="n">
+        <v>5833.333333333333</v>
+      </c>
+      <c r="P150" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>13</v>
+      </c>
+      <c r="R150" t="n">
+        <v>59.33333333333334</v>
+      </c>
+      <c r="S150" t="n">
+        <v>-68</v>
+      </c>
+      <c r="T150" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="151">
@@ -4210,7 +9816,7 @@
         <v>10</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E151" t="n">
         <v>6700</v>
@@ -4219,7 +9825,46 @@
         <v>53</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K151" t="n">
+        <v>2400</v>
+      </c>
+      <c r="L151" t="n">
+        <v>7300</v>
+      </c>
+      <c r="M151" t="n">
+        <v>5200</v>
+      </c>
+      <c r="N151" t="n">
+        <v>6300</v>
+      </c>
+      <c r="O151" t="n">
+        <v>4616.666666666667</v>
+      </c>
+      <c r="P151" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>73</v>
+      </c>
+      <c r="R151" t="n">
+        <v>63</v>
+      </c>
+      <c r="S151" t="n">
+        <v>29</v>
+      </c>
+      <c r="T151" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="152">
@@ -4235,7 +9880,7 @@
         <v>11</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E152" t="n">
         <v>10800</v>
@@ -4244,7 +9889,46 @@
         <v>36</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H152" t="n">
+        <v>4</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K152" t="n">
+        <v>6700</v>
+      </c>
+      <c r="L152" t="n">
+        <v>9200</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N152" t="n">
+        <v>6100</v>
+      </c>
+      <c r="O152" t="n">
+        <v>4866.666666666667</v>
+      </c>
+      <c r="P152" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>92</v>
+      </c>
+      <c r="R152" t="n">
+        <v>56.33333333333334</v>
+      </c>
+      <c r="S152" t="n">
+        <v>-17</v>
+      </c>
+      <c r="T152" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="153">
@@ -4260,7 +9944,7 @@
         <v>12</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E153" t="n">
         <v>8400</v>
@@ -4269,7 +9953,46 @@
         <v>28</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H153" t="n">
+        <v>4</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="n">
+        <v>10800</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1300</v>
+      </c>
+      <c r="N153" t="n">
+        <v>6633.333333333333</v>
+      </c>
+      <c r="O153" t="n">
+        <v>6283.333333333333</v>
+      </c>
+      <c r="P153" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>24</v>
+      </c>
+      <c r="R153" t="n">
+        <v>37.66666666666666</v>
+      </c>
+      <c r="S153" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T153" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="154">
@@ -4285,7 +10008,7 @@
         <v>1</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E154" t="n">
         <v>9000</v>
@@ -4294,7 +10017,46 @@
         <v>30</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K154" t="n">
+        <v>8400</v>
+      </c>
+      <c r="L154" t="n">
+        <v>6700</v>
+      </c>
+      <c r="M154" t="n">
+        <v>7300</v>
+      </c>
+      <c r="N154" t="n">
+        <v>8633.333333333334</v>
+      </c>
+      <c r="O154" t="n">
+        <v>7466.666666666667</v>
+      </c>
+      <c r="P154" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>53</v>
+      </c>
+      <c r="R154" t="n">
+        <v>39</v>
+      </c>
+      <c r="S154" t="n">
+        <v>2</v>
+      </c>
+      <c r="T154" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="155">
@@ -4310,7 +10072,7 @@
         <v>2</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E155" t="n">
         <v>9000</v>
@@ -4319,7 +10081,46 @@
         <v>30</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K155" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L155" t="n">
+        <v>10800</v>
+      </c>
+      <c r="M155" t="n">
+        <v>9200</v>
+      </c>
+      <c r="N155" t="n">
+        <v>9400</v>
+      </c>
+      <c r="O155" t="n">
+        <v>7750</v>
+      </c>
+      <c r="P155" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>36</v>
+      </c>
+      <c r="R155" t="n">
+        <v>31.33333333333333</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="156">
@@ -4335,7 +10136,7 @@
         <v>3</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E156" t="n">
         <v>8100</v>
@@ -4344,7 +10145,46 @@
         <v>27</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K156" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L156" t="n">
+        <v>8400</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N156" t="n">
+        <v>8800</v>
+      </c>
+      <c r="O156" t="n">
+        <v>7716.666666666667</v>
+      </c>
+      <c r="P156" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>28</v>
+      </c>
+      <c r="R156" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="S156" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T156" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="157">
@@ -4360,7 +10200,7 @@
         <v>4</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E157" t="n">
         <v>6900</v>
@@ -4369,7 +10209,46 @@
         <v>23</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J157" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K157" t="n">
+        <v>8100</v>
+      </c>
+      <c r="L157" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M157" t="n">
+        <v>6700</v>
+      </c>
+      <c r="N157" t="n">
+        <v>8700</v>
+      </c>
+      <c r="O157" t="n">
+        <v>8666.666666666666</v>
+      </c>
+      <c r="P157" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>30</v>
+      </c>
+      <c r="R157" t="n">
+        <v>29</v>
+      </c>
+      <c r="S157" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T157" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="158">
@@ -4385,7 +10264,7 @@
         <v>5</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E158" t="n">
         <v>4500</v>
@@ -4394,7 +10273,46 @@
         <v>15</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J158" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K158" t="n">
+        <v>6900</v>
+      </c>
+      <c r="L158" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M158" t="n">
+        <v>10800</v>
+      </c>
+      <c r="N158" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O158" t="n">
+        <v>8700</v>
+      </c>
+      <c r="P158" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>30</v>
+      </c>
+      <c r="R158" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="S158" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T158" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="159">
@@ -4410,7 +10328,7 @@
         <v>6</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E159" t="n">
         <v>5100</v>
@@ -4419,7 +10337,46 @@
         <v>17</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K159" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L159" t="n">
+        <v>8100</v>
+      </c>
+      <c r="M159" t="n">
+        <v>8400</v>
+      </c>
+      <c r="N159" t="n">
+        <v>6500</v>
+      </c>
+      <c r="O159" t="n">
+        <v>7650</v>
+      </c>
+      <c r="P159" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>27</v>
+      </c>
+      <c r="R159" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="S159" t="n">
+        <v>2</v>
+      </c>
+      <c r="T159" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="160">
@@ -4435,7 +10392,7 @@
         <v>7</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E160" t="n">
         <v>5100</v>
@@ -4444,7 +10401,46 @@
         <v>17</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J160" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K160" t="n">
+        <v>5100</v>
+      </c>
+      <c r="L160" t="n">
+        <v>6900</v>
+      </c>
+      <c r="M160" t="n">
+        <v>9000</v>
+      </c>
+      <c r="N160" t="n">
+        <v>5500</v>
+      </c>
+      <c r="O160" t="n">
+        <v>7100</v>
+      </c>
+      <c r="P160" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>23</v>
+      </c>
+      <c r="R160" t="n">
+        <v>18.33333333333333</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="161">
@@ -4460,7 +10456,7 @@
         <v>8</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E161" t="n">
         <v>3900</v>
@@ -4469,7 +10465,46 @@
         <v>13</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J161" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K161" t="n">
+        <v>5100</v>
+      </c>
+      <c r="L161" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M161" t="n">
+        <v>9000</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4900</v>
+      </c>
+      <c r="O161" t="n">
+        <v>6450</v>
+      </c>
+      <c r="P161" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>15</v>
+      </c>
+      <c r="R161" t="n">
+        <v>16.33333333333333</v>
+      </c>
+      <c r="S161" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T161" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="162">
@@ -4485,7 +10520,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E162" t="n">
         <v>4200</v>
@@ -4494,7 +10529,46 @@
         <v>14</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3</v>
+      </c>
+      <c r="I162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K162" t="n">
+        <v>3900</v>
+      </c>
+      <c r="L162" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M162" t="n">
+        <v>8100</v>
+      </c>
+      <c r="N162" t="n">
+        <v>4700</v>
+      </c>
+      <c r="O162" t="n">
+        <v>5600</v>
+      </c>
+      <c r="P162" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>17</v>
+      </c>
+      <c r="R162" t="n">
+        <v>15.66666666666667</v>
+      </c>
+      <c r="S162" t="n">
+        <v>1</v>
+      </c>
+      <c r="T162" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="163">
@@ -4510,7 +10584,7 @@
         <v>10</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E163" t="n">
         <v>4800</v>
@@ -4519,7 +10593,46 @@
         <v>16</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H163" t="n">
+        <v>4</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K163" t="n">
+        <v>4200</v>
+      </c>
+      <c r="L163" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M163" t="n">
+        <v>6900</v>
+      </c>
+      <c r="N163" t="n">
+        <v>4400</v>
+      </c>
+      <c r="O163" t="n">
+        <v>4950</v>
+      </c>
+      <c r="P163" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>17</v>
+      </c>
+      <c r="R163" t="n">
+        <v>14.66666666666667</v>
+      </c>
+      <c r="S163" t="n">
+        <v>2</v>
+      </c>
+      <c r="T163" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="164">
@@ -4535,7 +10648,7 @@
         <v>11</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E164" t="n">
         <v>7800</v>
@@ -4544,7 +10657,46 @@
         <v>26</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H164" t="n">
+        <v>4</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K164" t="n">
+        <v>4800</v>
+      </c>
+      <c r="L164" t="n">
+        <v>3900</v>
+      </c>
+      <c r="M164" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N164" t="n">
+        <v>4300</v>
+      </c>
+      <c r="O164" t="n">
+        <v>4600</v>
+      </c>
+      <c r="P164" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>13</v>
+      </c>
+      <c r="R164" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="165">
@@ -4560,7 +10712,7 @@
         <v>12</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E165" t="n">
         <v>4800</v>
@@ -4569,7 +10721,46 @@
         <v>16</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4</v>
+      </c>
+      <c r="I165" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>7800</v>
+      </c>
+      <c r="L165" t="n">
+        <v>4200</v>
+      </c>
+      <c r="M165" t="n">
+        <v>5100</v>
+      </c>
+      <c r="N165" t="n">
+        <v>5600</v>
+      </c>
+      <c r="O165" t="n">
+        <v>5150</v>
+      </c>
+      <c r="P165" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>14</v>
+      </c>
+      <c r="R165" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="S165" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T165" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/recettes_produit.xlsx
+++ b/data/processed/recettes_produit.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T165"/>
+  <dimension ref="A1:T171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6407,10 +6407,10 @@
         <v>45626</v>
       </c>
       <c r="E96" t="n">
-        <v>65216</v>
+        <v>65016</v>
       </c>
       <c r="F96" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>45626</v>
@@ -6449,7 +6449,7 @@
         <v>95.33333333333333</v>
       </c>
       <c r="S96" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="T96" t="n">
         <v>22</v>
@@ -6471,10 +6471,10 @@
         <v>45657</v>
       </c>
       <c r="E97" t="n">
-        <v>67406</v>
+        <v>66206</v>
       </c>
       <c r="F97" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>45657</v>
@@ -6489,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>65216</v>
+        <v>65016</v>
       </c>
       <c r="L97" t="n">
         <v>50886</v>
@@ -6498,22 +6498,22 @@
         <v>253987</v>
       </c>
       <c r="N97" t="n">
-        <v>63619</v>
+        <v>63552.33333333334</v>
       </c>
       <c r="O97" t="n">
-        <v>95331.16666666667</v>
+        <v>95297.83333333333</v>
       </c>
       <c r="P97" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q97" t="n">
         <v>72</v>
       </c>
       <c r="R97" t="n">
-        <v>95.33333333333333</v>
+        <v>95</v>
       </c>
       <c r="S97" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="T97" t="n">
         <v>23</v>
@@ -6553,7 +6553,7 @@
         <v>0.8660254037844387</v>
       </c>
       <c r="K98" t="n">
-        <v>67406</v>
+        <v>66206</v>
       </c>
       <c r="L98" t="n">
         <v>74755</v>
@@ -6562,22 +6562,22 @@
         <v>63935</v>
       </c>
       <c r="N98" t="n">
-        <v>69125.66666666667</v>
+        <v>68659</v>
       </c>
       <c r="O98" t="n">
-        <v>64234.33333333334</v>
+        <v>64001</v>
       </c>
       <c r="P98" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="Q98" t="n">
         <v>115</v>
       </c>
       <c r="R98" t="n">
-        <v>100.6666666666667</v>
+        <v>98.33333333333333</v>
       </c>
       <c r="S98" t="n">
-        <v>-29</v>
+        <v>-23</v>
       </c>
       <c r="T98" t="n">
         <v>24</v>
@@ -6620,25 +6620,25 @@
         <v>42291</v>
       </c>
       <c r="L99" t="n">
-        <v>65216</v>
+        <v>65016</v>
       </c>
       <c r="M99" t="n">
         <v>63208</v>
       </c>
       <c r="N99" t="n">
-        <v>58304.33333333334</v>
+        <v>57837.66666666666</v>
       </c>
       <c r="O99" t="n">
-        <v>60627</v>
+        <v>60393.66666666666</v>
       </c>
       <c r="P99" t="n">
         <v>59</v>
       </c>
       <c r="Q99" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R99" t="n">
-        <v>82</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="S99" t="n">
         <v>-3</v>
@@ -6663,10 +6663,10 @@
         <v>45747</v>
       </c>
       <c r="E100" t="n">
-        <v>55776</v>
+        <v>55576</v>
       </c>
       <c r="F100" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>45747</v>
@@ -6684,28 +6684,28 @@
         <v>42880</v>
       </c>
       <c r="L100" t="n">
-        <v>67406</v>
+        <v>66206</v>
       </c>
       <c r="M100" t="n">
         <v>50886</v>
       </c>
       <c r="N100" t="n">
-        <v>50859</v>
+        <v>50459</v>
       </c>
       <c r="O100" t="n">
-        <v>57239</v>
+        <v>57005.66666666666</v>
       </c>
       <c r="P100" t="n">
         <v>56</v>
       </c>
       <c r="Q100" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="R100" t="n">
-        <v>67.66666666666667</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="S100" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T100" t="n">
         <v>26</v>
@@ -6745,7 +6745,7 @@
         <v>-0.4999999999999998</v>
       </c>
       <c r="K101" t="n">
-        <v>55776</v>
+        <v>55576</v>
       </c>
       <c r="L101" t="n">
         <v>42291</v>
@@ -6754,22 +6754,22 @@
         <v>74755</v>
       </c>
       <c r="N101" t="n">
-        <v>46982.33333333334</v>
+        <v>46915.66666666666</v>
       </c>
       <c r="O101" t="n">
-        <v>58054</v>
+        <v>57787.33333333334</v>
       </c>
       <c r="P101" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q101" t="n">
         <v>59</v>
       </c>
       <c r="R101" t="n">
-        <v>64.66666666666667</v>
+        <v>64.33333333333333</v>
       </c>
       <c r="S101" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T101" t="n">
         <v>27</v>
@@ -6815,13 +6815,13 @@
         <v>42880</v>
       </c>
       <c r="M102" t="n">
-        <v>65216</v>
+        <v>65016</v>
       </c>
       <c r="N102" t="n">
-        <v>49990.33333333334</v>
+        <v>49923.66666666666</v>
       </c>
       <c r="O102" t="n">
-        <v>54147.33333333334</v>
+        <v>53880.66666666666</v>
       </c>
       <c r="P102" t="n">
         <v>68</v>
@@ -6830,7 +6830,7 @@
         <v>56</v>
       </c>
       <c r="R102" t="n">
-        <v>67.66666666666667</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -6876,25 +6876,25 @@
         <v>53420</v>
       </c>
       <c r="L103" t="n">
-        <v>55776</v>
+        <v>55576</v>
       </c>
       <c r="M103" t="n">
-        <v>67406</v>
+        <v>66206</v>
       </c>
       <c r="N103" t="n">
-        <v>53503.66666666666</v>
+        <v>53437</v>
       </c>
       <c r="O103" t="n">
-        <v>52181.33333333334</v>
+        <v>51948</v>
       </c>
       <c r="P103" t="n">
         <v>72</v>
       </c>
       <c r="Q103" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R103" t="n">
-        <v>73</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="S103" t="n">
         <v>-13</v>
@@ -6949,7 +6949,7 @@
         <v>48900.66666666666</v>
       </c>
       <c r="O104" t="n">
-        <v>47941.5</v>
+        <v>47908.16666666666</v>
       </c>
       <c r="P104" t="n">
         <v>59</v>
@@ -7013,7 +7013,7 @@
         <v>47252.66666666666</v>
       </c>
       <c r="O105" t="n">
-        <v>48621.5</v>
+        <v>48588.16666666666</v>
       </c>
       <c r="P105" t="n">
         <v>59</v>
@@ -7047,10 +7047,10 @@
         <v>45930</v>
       </c>
       <c r="E106" t="n">
-        <v>40080</v>
+        <v>39880</v>
       </c>
       <c r="F106" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>45930</v>
@@ -7071,13 +7071,13 @@
         <v>41967</v>
       </c>
       <c r="M106" t="n">
-        <v>55776</v>
+        <v>55576</v>
       </c>
       <c r="N106" t="n">
         <v>41729.33333333334</v>
       </c>
       <c r="O106" t="n">
-        <v>47616.5</v>
+        <v>47583.16666666666</v>
       </c>
       <c r="P106" t="n">
         <v>51</v>
@@ -7089,7 +7089,7 @@
         <v>56.33333333333334</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="n">
         <v>32</v>
@@ -7111,10 +7111,10 @@
         <v>45961</v>
       </c>
       <c r="E107" t="n">
-        <v>65171</v>
+        <v>64971</v>
       </c>
       <c r="F107" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>45961</v>
@@ -7129,7 +7129,7 @@
         <v>0.5000000000000001</v>
       </c>
       <c r="K107" t="n">
-        <v>40080</v>
+        <v>39880</v>
       </c>
       <c r="L107" t="n">
         <v>46371</v>
@@ -7138,19 +7138,19 @@
         <v>51315</v>
       </c>
       <c r="N107" t="n">
-        <v>41100.33333333334</v>
+        <v>41033.66666666666</v>
       </c>
       <c r="O107" t="n">
-        <v>45000.5</v>
+        <v>44967.16666666666</v>
       </c>
       <c r="P107" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q107" t="n">
         <v>59</v>
       </c>
       <c r="R107" t="n">
-        <v>57</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="S107" t="n">
         <v>12</v>
@@ -7175,10 +7175,10 @@
         <v>45991</v>
       </c>
       <c r="E108" t="n">
-        <v>37311</v>
+        <v>36911</v>
       </c>
       <c r="F108" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>45991</v>
@@ -7193,7 +7193,7 @@
         <v>0.8660254037844384</v>
       </c>
       <c r="K108" t="n">
-        <v>65171</v>
+        <v>64971</v>
       </c>
       <c r="L108" t="n">
         <v>36850</v>
@@ -7202,22 +7202,22 @@
         <v>53420</v>
       </c>
       <c r="N108" t="n">
-        <v>47367</v>
+        <v>47233.66666666666</v>
       </c>
       <c r="O108" t="n">
-        <v>47309.83333333334</v>
+        <v>47243.16666666666</v>
       </c>
       <c r="P108" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q108" t="n">
         <v>51</v>
       </c>
       <c r="R108" t="n">
-        <v>61.66666666666666</v>
+        <v>61</v>
       </c>
       <c r="S108" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="T108" t="n">
         <v>34</v>
@@ -7257,31 +7257,31 @@
         <v>1</v>
       </c>
       <c r="K109" t="n">
-        <v>37311</v>
+        <v>36911</v>
       </c>
       <c r="L109" t="n">
-        <v>40080</v>
+        <v>39880</v>
       </c>
       <c r="M109" t="n">
         <v>41967</v>
       </c>
       <c r="N109" t="n">
-        <v>47520.66666666666</v>
+        <v>47254</v>
       </c>
       <c r="O109" t="n">
-        <v>44625</v>
+        <v>44491.66666666666</v>
       </c>
       <c r="P109" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q109" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R109" t="n">
-        <v>63.66666666666666</v>
+        <v>62.33333333333334</v>
       </c>
       <c r="S109" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T109" t="n">
         <v>35</v>
@@ -7290,35 +7290,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>45077</v>
+        <v>45626</v>
       </c>
       <c r="E110" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>45077</v>
+        <v>45626</v>
       </c>
       <c r="H110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.8660254037844387</v>
+        <v>0.8660254037844384</v>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
@@ -7336,38 +7336,38 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F111" t="n">
         <v>6</v>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>45107</v>
-      </c>
-      <c r="E111" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F111" t="n">
-        <v>1</v>
-      </c>
       <c r="G111" s="3" t="n">
-        <v>45107</v>
+        <v>45657</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>1.224646799147353e-16</v>
+        <v>-2.449293598294706e-16</v>
       </c>
       <c r="J111" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
@@ -7379,7 +7379,7 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T111" t="n">
         <v>1</v>
@@ -7388,50 +7388,50 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>45230</v>
+        <v>45747</v>
       </c>
       <c r="E112" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>45230</v>
+        <v>45747</v>
       </c>
       <c r="H112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.8660254037844386</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5000000000000001</v>
+        <v>6.123233995736766e-17</v>
       </c>
       <c r="K112" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T112" t="n">
         <v>2</v>
@@ -7440,45 +7440,45 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>45322</v>
+        <v>45930</v>
       </c>
       <c r="E113" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45322</v>
+        <v>45930</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4999999999999999</v>
+        <v>-1</v>
       </c>
       <c r="J113" t="n">
-        <v>0.8660254037844387</v>
+        <v>-1.83697019872103e-16</v>
       </c>
       <c r="K113" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="L113" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>3000</v>
+        <v>533.3333333333334</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
@@ -7488,10 +7488,10 @@
         <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>1</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
         <v>3</v>
@@ -7500,58 +7500,58 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C114" t="n">
+        <v>10</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="E114" t="n">
+        <v>200</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="H114" t="n">
         <v>4</v>
       </c>
-      <c r="D114" s="2" t="n">
-        <v>45412</v>
-      </c>
-      <c r="E114" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F114" t="n">
-        <v>3</v>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>45412</v>
-      </c>
-      <c r="H114" t="n">
-        <v>2</v>
-      </c>
       <c r="I114" t="n">
-        <v>0.8660254037844387</v>
+        <v>-0.8660254037844386</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.4999999999999998</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K114" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="L114" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
-        <v>2666.666666666667</v>
+        <v>533.3333333333334</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R114" t="n">
-        <v>1.333333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="S114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
         <v>4</v>
@@ -7560,58 +7560,58 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>45443</v>
+        <v>45991</v>
       </c>
       <c r="E115" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>45443</v>
+        <v>45991</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.8660254037844387</v>
+        <v>0.8660254037844384</v>
       </c>
       <c r="K115" t="n">
-        <v>10000</v>
+        <v>200</v>
       </c>
       <c r="L115" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q115" t="n">
         <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S115" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="T115" t="n">
         <v>5</v>
@@ -7624,61 +7624,43 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>45473</v>
+        <v>45077</v>
       </c>
       <c r="E116" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>45473</v>
+        <v>45077</v>
       </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
       <c r="I116" t="n">
-        <v>1.224646799147353e-16</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K116" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L116" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N116" t="n">
-        <v>5000</v>
-      </c>
-      <c r="O116" t="n">
-        <v>4000</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>2</v>
-      </c>
-      <c r="R116" t="n">
-        <v>2</v>
-      </c>
-      <c r="S116" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="n">
         <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -7688,61 +7670,49 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>45504</v>
+        <v>45107</v>
       </c>
       <c r="E117" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>45504</v>
+        <v>45107</v>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4999999999999997</v>
+        <v>1.224646799147353e-16</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.8660254037844388</v>
+        <v>-1</v>
       </c>
       <c r="K117" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L117" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M117" t="n">
         <v>3000</v>
       </c>
-      <c r="N117" t="n">
-        <v>4666.666666666667</v>
-      </c>
-      <c r="O117" t="n">
-        <v>3666.666666666667</v>
-      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
       <c r="P117" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" t="n">
-        <v>3</v>
-      </c>
-      <c r="R117" t="n">
-        <v>1.666666666666667</v>
-      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
       <c r="S117" t="n">
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -7752,61 +7722,49 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>45535</v>
+        <v>45230</v>
       </c>
       <c r="E118" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>45535</v>
+        <v>45230</v>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.8660254037844385</v>
+        <v>-0.8660254037844386</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.5000000000000004</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K118" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L118" t="n">
         <v>3000</v>
       </c>
-      <c r="M118" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N118" t="n">
-        <v>1666.666666666667</v>
-      </c>
-      <c r="O118" t="n">
-        <v>3333.333333333333</v>
-      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>1</v>
-      </c>
-      <c r="R118" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
       <c r="S118" t="n">
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -7819,58 +7777,54 @@
         <v>2024</v>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>45596</v>
+        <v>45322</v>
       </c>
       <c r="E119" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>45322</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L119" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="n">
         <v>3</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>45596</v>
-      </c>
-      <c r="H119" t="n">
-        <v>4</v>
-      </c>
-      <c r="I119" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.5000000000000001</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L119" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M119" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N119" t="n">
-        <v>1333.333333333333</v>
-      </c>
-      <c r="O119" t="n">
-        <v>3166.666666666667</v>
-      </c>
-      <c r="P119" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>1</v>
-      </c>
-      <c r="R119" t="n">
-        <v>1</v>
-      </c>
-      <c r="S119" t="n">
-        <v>2</v>
-      </c>
-      <c r="T119" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="120">
@@ -7880,61 +7834,57 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>45688</v>
+        <v>45412</v>
       </c>
       <c r="E120" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F120" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>45412</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L120" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
         <v>4</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>45688</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="K120" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L120" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M120" t="n">
-        <v>10000</v>
-      </c>
-      <c r="N120" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O120" t="n">
-        <v>3833.333333333333</v>
-      </c>
-      <c r="P120" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>1</v>
-      </c>
-      <c r="R120" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1</v>
-      </c>
-      <c r="T120" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="121">
@@ -7944,61 +7894,57 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>45443</v>
+      </c>
+      <c r="H121" t="n">
         <v>2</v>
       </c>
-      <c r="D121" s="2" t="n">
-        <v>45716</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="I121" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K121" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L121" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
         <v>5000</v>
       </c>
-      <c r="F121" t="n">
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
         <v>3</v>
       </c>
-      <c r="G121" s="3" t="n">
-        <v>45716</v>
-      </c>
-      <c r="H121" t="n">
-        <v>1</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0.5000000000000001</v>
-      </c>
-      <c r="K121" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L121" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M121" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N121" t="n">
-        <v>5333.333333333333</v>
-      </c>
-      <c r="O121" t="n">
-        <v>3500</v>
-      </c>
-      <c r="P121" t="n">
-        <v>4</v>
-      </c>
       <c r="Q121" t="n">
         <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>2.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="S121" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T121" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -8008,61 +7954,61 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>45808</v>
+        <v>45473</v>
       </c>
       <c r="E122" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="F122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>45808</v>
+        <v>45473</v>
       </c>
       <c r="H122" t="n">
         <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4999999999999999</v>
+        <v>1.224646799147353e-16</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.8660254037844387</v>
+        <v>-1</v>
       </c>
       <c r="K122" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L122" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N122" t="n">
         <v>5000</v>
       </c>
-      <c r="L122" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M122" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N122" t="n">
-        <v>6333.333333333333</v>
-      </c>
       <c r="O122" t="n">
-        <v>3833.333333333333</v>
+        <v>4000</v>
       </c>
       <c r="P122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R122" t="n">
-        <v>3.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -8072,61 +8018,61 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>45838</v>
+        <v>45504</v>
       </c>
       <c r="E123" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>45504</v>
+      </c>
+      <c r="H123" t="n">
         <v>3</v>
       </c>
-      <c r="G123" s="3" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H123" t="n">
-        <v>2</v>
-      </c>
       <c r="I123" t="n">
-        <v>1.224646799147353e-16</v>
+        <v>-0.4999999999999997</v>
       </c>
       <c r="J123" t="n">
-        <v>-1</v>
+        <v>-0.8660254037844388</v>
       </c>
       <c r="K123" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="L123" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="M123" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="N123" t="n">
-        <v>6333.333333333333</v>
+        <v>4666.666666666667</v>
       </c>
       <c r="O123" t="n">
-        <v>4666.666666666667</v>
+        <v>3666.666666666667</v>
       </c>
       <c r="P123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R123" t="n">
-        <v>3.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -8136,61 +8082,61 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>45869</v>
+        <v>45535</v>
       </c>
       <c r="E124" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>45869</v>
+        <v>45535</v>
       </c>
       <c r="H124" t="n">
         <v>3</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4999999999999997</v>
+        <v>-0.8660254037844385</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.8660254037844388</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="K124" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="L124" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="M124" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N124" t="n">
-        <v>5000</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="O124" t="n">
-        <v>5166.666666666667</v>
+        <v>3333.333333333333</v>
       </c>
       <c r="P124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>3.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S124" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -8200,61 +8146,61 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>45900</v>
+        <v>45596</v>
       </c>
       <c r="E125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K125" t="n">
         <v>2000</v>
       </c>
-      <c r="F125" t="n">
+      <c r="L125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1333.333333333333</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3166.666666666667</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="n">
         <v>2</v>
       </c>
-      <c r="G125" s="3" t="n">
-        <v>45900</v>
-      </c>
-      <c r="H125" t="n">
-        <v>3</v>
-      </c>
-      <c r="I125" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="J125" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L125" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M125" t="n">
-        <v>6000</v>
-      </c>
-      <c r="N125" t="n">
-        <v>3666.666666666667</v>
-      </c>
-      <c r="O125" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>4</v>
-      </c>
-      <c r="R125" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="S125" t="n">
-        <v>1</v>
-      </c>
       <c r="T125" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
@@ -8267,58 +8213,58 @@
         <v>2025</v>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>45930</v>
+        <v>45688</v>
       </c>
       <c r="E126" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>45930</v>
+        <v>45688</v>
       </c>
       <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K126" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M126" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O126" t="n">
+        <v>3833.333333333333</v>
+      </c>
+      <c r="P126" t="n">
         <v>3</v>
       </c>
-      <c r="I126" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J126" t="n">
-        <v>-1.83697019872103e-16</v>
-      </c>
-      <c r="K126" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L126" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M126" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N126" t="n">
-        <v>2333.333333333333</v>
-      </c>
-      <c r="O126" t="n">
-        <v>4333.333333333333</v>
-      </c>
-      <c r="P126" t="n">
-        <v>2</v>
-      </c>
       <c r="Q126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -8331,58 +8277,58 @@
         <v>2025</v>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>45961</v>
+        <v>45716</v>
       </c>
       <c r="E127" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>45961</v>
+        <v>45716</v>
       </c>
       <c r="H127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.8660254037844386</v>
+        <v>0.8660254037844386</v>
       </c>
       <c r="J127" t="n">
         <v>0.5000000000000001</v>
       </c>
       <c r="K127" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L127" t="n">
         <v>2000</v>
       </c>
-      <c r="L127" t="n">
-        <v>1000</v>
-      </c>
       <c r="M127" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="N127" t="n">
-        <v>1666.666666666667</v>
+        <v>5333.333333333333</v>
       </c>
       <c r="O127" t="n">
-        <v>3333.333333333333</v>
+        <v>3500</v>
       </c>
       <c r="P127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q127" t="n">
         <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>1.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T127" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
@@ -8395,58 +8341,58 @@
         <v>2025</v>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>45991</v>
+        <v>45808</v>
       </c>
       <c r="E128" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F128" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>45808</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L128" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N128" t="n">
+        <v>6333.333333333333</v>
+      </c>
+      <c r="O128" t="n">
+        <v>3833.333333333333</v>
+      </c>
+      <c r="P128" t="n">
         <v>3</v>
       </c>
-      <c r="G128" s="3" t="n">
-        <v>45991</v>
-      </c>
-      <c r="H128" t="n">
-        <v>4</v>
-      </c>
-      <c r="I128" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0.8660254037844384</v>
-      </c>
-      <c r="K128" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L128" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M128" t="n">
-        <v>6000</v>
-      </c>
-      <c r="N128" t="n">
-        <v>2333.333333333333</v>
-      </c>
-      <c r="O128" t="n">
-        <v>3000</v>
-      </c>
-      <c r="P128" t="n">
-        <v>2</v>
-      </c>
       <c r="Q128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R128" t="n">
-        <v>2</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
       </c>
       <c r="T128" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129">
@@ -8459,388 +8405,442 @@
         <v>2025</v>
       </c>
       <c r="C129" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>46022</v>
+        <v>45838</v>
       </c>
       <c r="E129" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F129" t="n">
+        <v>3</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>45838</v>
+      </c>
+      <c r="H129" t="n">
         <v>2</v>
       </c>
-      <c r="G129" s="3" t="n">
-        <v>46022</v>
-      </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L129" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N129" t="n">
+        <v>6333.333333333333</v>
+      </c>
+      <c r="O129" t="n">
+        <v>4666.666666666667</v>
+      </c>
+      <c r="P129" t="n">
         <v>4</v>
       </c>
-      <c r="I129" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1</v>
-      </c>
-      <c r="K129" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L129" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M129" t="n">
-        <v>4000</v>
-      </c>
-      <c r="N129" t="n">
-        <v>2666.666666666667</v>
-      </c>
-      <c r="O129" t="n">
-        <v>2500</v>
-      </c>
-      <c r="P129" t="n">
-        <v>3</v>
-      </c>
       <c r="Q129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
-        <v>2.333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="S129" t="n">
         <v>-1</v>
       </c>
       <c r="T129" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>44957</v>
+        <v>45869</v>
       </c>
       <c r="E130" t="n">
-        <v>3800</v>
+        <v>1000</v>
       </c>
       <c r="F130" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>44957</v>
+        <v>45869</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.4999999999999997</v>
       </c>
       <c r="J130" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K130" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L130" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M130" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N130" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O130" t="n">
+        <v>5166.666666666667</v>
+      </c>
+      <c r="P130" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>3</v>
+      </c>
+      <c r="R130" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S130" t="n">
+        <v>-2</v>
+      </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C131" t="n">
+        <v>8</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F131" t="n">
         <v>2</v>
       </c>
-      <c r="D131" s="2" t="n">
-        <v>44985</v>
-      </c>
-      <c r="E131" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F131" t="n">
-        <v>45</v>
-      </c>
       <c r="G131" s="3" t="n">
-        <v>44985</v>
+        <v>45900</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I131" t="n">
-        <v>0.8660254037844386</v>
+        <v>-0.8660254037844385</v>
       </c>
       <c r="J131" t="n">
-        <v>0.5000000000000001</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="K131" t="n">
-        <v>3800</v>
-      </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="L131" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M131" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N131" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="O131" t="n">
+        <v>5000</v>
+      </c>
       <c r="P131" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>4</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2.666666666666667</v>
+      </c>
       <c r="S131" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C132" t="n">
+        <v>9</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="H132" t="n">
         <v>3</v>
       </c>
-      <c r="D132" s="2" t="n">
-        <v>45016</v>
-      </c>
-      <c r="E132" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F132" t="n">
-        <v>36</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>45016</v>
-      </c>
-      <c r="H132" t="n">
-        <v>1</v>
-      </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J132" t="n">
-        <v>6.123233995736766e-17</v>
+        <v>-1.83697019872103e-16</v>
       </c>
       <c r="K132" t="n">
-        <v>4500</v>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M132" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="O132" t="n">
+        <v>4333.333333333333</v>
+      </c>
       <c r="P132" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>3</v>
+      </c>
+      <c r="R132" t="n">
+        <v>2</v>
+      </c>
       <c r="S132" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C133" t="n">
+        <v>10</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="H133" t="n">
         <v>4</v>
       </c>
-      <c r="D133" s="2" t="n">
-        <v>45046</v>
-      </c>
-      <c r="E133" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F133" t="n">
-        <v>25</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>45046</v>
-      </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M133" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1666.666666666667</v>
+      </c>
+      <c r="O133" t="n">
+        <v>3333.333333333333</v>
+      </c>
+      <c r="P133" t="n">
         <v>2</v>
       </c>
-      <c r="I133" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="J133" t="n">
-        <v>-0.4999999999999998</v>
-      </c>
-      <c r="K133" t="n">
-        <v>3600</v>
-      </c>
-      <c r="L133" t="n">
-        <v>3800</v>
-      </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="n">
-        <v>3966.666666666667</v>
-      </c>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="n">
-        <v>36</v>
-      </c>
       <c r="Q133" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="R133" t="n">
-        <v>39.66666666666666</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S133" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>45077</v>
+        <v>45991</v>
       </c>
       <c r="E134" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="F134" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>45077</v>
+        <v>45991</v>
       </c>
       <c r="H134" t="n">
+        <v>4</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L134" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M134" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="O134" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P134" t="n">
         <v>2</v>
       </c>
-      <c r="I134" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="J134" t="n">
-        <v>-0.8660254037844387</v>
-      </c>
-      <c r="K134" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L134" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="n">
-        <v>3533.333333333333</v>
-      </c>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="n">
-        <v>25</v>
-      </c>
       <c r="Q134" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="R134" t="n">
-        <v>35.33333333333334</v>
+        <v>2</v>
       </c>
       <c r="S134" t="n">
         <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>45107</v>
+        <v>46022</v>
       </c>
       <c r="E135" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="F135" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>45107</v>
+        <v>46022</v>
       </c>
       <c r="H135" t="n">
+        <v>4</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L135" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M135" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2666.666666666667</v>
+      </c>
+      <c r="O135" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P135" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q135" t="n">
         <v>2</v>
       </c>
-      <c r="I135" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="J135" t="n">
+      <c r="R135" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="S135" t="n">
         <v>-1</v>
       </c>
-      <c r="K135" t="n">
-        <v>2600</v>
-      </c>
-      <c r="L135" t="n">
-        <v>3600</v>
-      </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="n">
-        <v>2900</v>
-      </c>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>36</v>
-      </c>
-      <c r="R135" t="n">
-        <v>29</v>
-      </c>
-      <c r="S135" t="n">
-        <v>-15</v>
-      </c>
       <c r="T135" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136">
@@ -8853,58 +8853,40 @@
         <v>2023</v>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>45138</v>
+        <v>44957</v>
       </c>
       <c r="E136" t="n">
-        <v>2100</v>
+        <v>3800</v>
       </c>
       <c r="F136" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>45138</v>
+        <v>44957</v>
       </c>
       <c r="H136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4999999999999997</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.8660254037844388</v>
-      </c>
-      <c r="K136" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L136" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M136" t="n">
-        <v>3800</v>
-      </c>
-      <c r="N136" t="n">
-        <v>2066.666666666667</v>
-      </c>
-      <c r="O136" t="n">
-        <v>3016.666666666667</v>
-      </c>
-      <c r="P136" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>25</v>
-      </c>
-      <c r="R136" t="n">
-        <v>20.66666666666667</v>
-      </c>
-      <c r="S136" t="n">
-        <v>10</v>
-      </c>
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8917,58 +8899,46 @@
         <v>2023</v>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>45169</v>
+        <v>44985</v>
       </c>
       <c r="E137" t="n">
-        <v>7600</v>
+        <v>4500</v>
       </c>
       <c r="F137" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>45169</v>
+        <v>44985</v>
       </c>
       <c r="H137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.8660254037844385</v>
+        <v>0.8660254037844386</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.5000000000000004</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K137" t="n">
-        <v>2100</v>
-      </c>
-      <c r="L137" t="n">
-        <v>2600</v>
-      </c>
-      <c r="M137" t="n">
-        <v>4500</v>
-      </c>
-      <c r="N137" t="n">
-        <v>1933.333333333333</v>
-      </c>
-      <c r="O137" t="n">
-        <v>2733.333333333333</v>
-      </c>
+        <v>3800</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
       <c r="P137" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>26</v>
-      </c>
-      <c r="R137" t="n">
-        <v>19.33333333333333</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="T137" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -8981,58 +8951,46 @@
         <v>2023</v>
       </c>
       <c r="C138" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>45199</v>
+        <v>45016</v>
       </c>
       <c r="E138" t="n">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="F138" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>45199</v>
+        <v>45016</v>
       </c>
       <c r="H138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.83697019872103e-16</v>
+        <v>6.123233995736766e-17</v>
       </c>
       <c r="K138" t="n">
-        <v>7600</v>
-      </c>
-      <c r="L138" t="n">
-        <v>1100</v>
-      </c>
-      <c r="M138" t="n">
-        <v>3600</v>
-      </c>
-      <c r="N138" t="n">
-        <v>3600</v>
-      </c>
-      <c r="O138" t="n">
-        <v>3250</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>11</v>
-      </c>
-      <c r="R138" t="n">
-        <v>36</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>-48</v>
+        <v>-9</v>
       </c>
       <c r="T138" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -9045,58 +9003,54 @@
         <v>2023</v>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>45230</v>
+        <v>45046</v>
       </c>
       <c r="E139" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="F139" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>45230</v>
+        <v>45046</v>
       </c>
       <c r="H139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.8660254037844386</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="J139" t="n">
-        <v>0.5000000000000001</v>
+        <v>-0.4999999999999998</v>
       </c>
       <c r="K139" t="n">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="L139" t="n">
-        <v>2100</v>
-      </c>
-      <c r="M139" t="n">
-        <v>2500</v>
-      </c>
+        <v>3800</v>
+      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>4166.666666666667</v>
-      </c>
-      <c r="O139" t="n">
-        <v>3116.666666666667</v>
-      </c>
+        <v>3966.666666666667</v>
+      </c>
+      <c r="O139" t="inlineStr"/>
       <c r="P139" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q139" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="R139" t="n">
-        <v>41.66666666666666</v>
+        <v>39.66666666666666</v>
       </c>
       <c r="S139" t="n">
-        <v>22</v>
+        <v>-11</v>
       </c>
       <c r="T139" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -9109,58 +9063,54 @@
         <v>2023</v>
       </c>
       <c r="C140" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>45260</v>
+        <v>45077</v>
       </c>
       <c r="E140" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="F140" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>45260</v>
+        <v>45077</v>
       </c>
       <c r="H140" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L140" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>3533.333333333333</v>
+      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>45</v>
+      </c>
+      <c r="R140" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
         <v>4</v>
-      </c>
-      <c r="I140" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0.8660254037844384</v>
-      </c>
-      <c r="K140" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L140" t="n">
-        <v>7600</v>
-      </c>
-      <c r="M140" t="n">
-        <v>2600</v>
-      </c>
-      <c r="N140" t="n">
-        <v>5133.333333333333</v>
-      </c>
-      <c r="O140" t="n">
-        <v>3533.333333333333</v>
-      </c>
-      <c r="P140" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>76</v>
-      </c>
-      <c r="R140" t="n">
-        <v>51.33333333333334</v>
-      </c>
-      <c r="S140" t="n">
-        <v>-34</v>
-      </c>
-      <c r="T140" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="141">
@@ -9173,58 +9123,54 @@
         <v>2023</v>
       </c>
       <c r="C141" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>45291</v>
+        <v>45107</v>
       </c>
       <c r="E141" t="n">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="F141" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>45291</v>
+        <v>45107</v>
       </c>
       <c r="H141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I141" t="n">
-        <v>-2.449293598294706e-16</v>
+        <v>1.224646799147353e-16</v>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K141" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="L141" t="n">
-        <v>2800</v>
-      </c>
-      <c r="M141" t="n">
-        <v>1100</v>
-      </c>
+        <v>3600</v>
+      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
-        <v>3133.333333333333</v>
-      </c>
-      <c r="O141" t="n">
-        <v>3366.666666666667</v>
-      </c>
+        <v>2900</v>
+      </c>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q141" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R141" t="n">
-        <v>31.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="S141" t="n">
-        <v>12</v>
+        <v>-15</v>
       </c>
       <c r="T141" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -9234,61 +9180,61 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>45322</v>
+        <v>45138</v>
       </c>
       <c r="E142" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="F142" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>45322</v>
+        <v>45138</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.4999999999999997</v>
       </c>
       <c r="J142" t="n">
-        <v>0.8660254037844387</v>
+        <v>-0.8660254037844388</v>
       </c>
       <c r="K142" t="n">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="L142" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="M142" t="n">
-        <v>2100</v>
+        <v>3800</v>
       </c>
       <c r="N142" t="n">
-        <v>3133.333333333333</v>
+        <v>2066.666666666667</v>
       </c>
       <c r="O142" t="n">
-        <v>3650</v>
+        <v>3016.666666666667</v>
       </c>
       <c r="P142" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="Q142" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="R142" t="n">
-        <v>31.33333333333333</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="S142" t="n">
-        <v>-9</v>
+        <v>10</v>
       </c>
       <c r="T142" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
@@ -9298,61 +9244,61 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>45351</v>
+        <v>45169</v>
       </c>
       <c r="E143" t="n">
-        <v>1800</v>
+        <v>7600</v>
       </c>
       <c r="F143" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>45351</v>
+        <v>45169</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8660254037844386</v>
+        <v>-0.8660254037844385</v>
       </c>
       <c r="J143" t="n">
-        <v>0.5000000000000001</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="K143" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="L143" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="M143" t="n">
-        <v>7600</v>
+        <v>4500</v>
       </c>
       <c r="N143" t="n">
-        <v>2100</v>
+        <v>1933.333333333333</v>
       </c>
       <c r="O143" t="n">
-        <v>3616.666666666667</v>
+        <v>2733.333333333333</v>
       </c>
       <c r="P143" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q143" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="R143" t="n">
-        <v>21</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="S143" t="n">
-        <v>-1</v>
+        <v>55</v>
       </c>
       <c r="T143" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -9362,61 +9308,61 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C144" t="n">
+        <v>9</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>45199</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F144" t="n">
+        <v>28</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>45199</v>
+      </c>
+      <c r="H144" t="n">
         <v>3</v>
       </c>
-      <c r="D144" s="2" t="n">
-        <v>45382</v>
-      </c>
-      <c r="E144" t="n">
-        <v>9700</v>
-      </c>
-      <c r="F144" t="n">
-        <v>97</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>45382</v>
-      </c>
-      <c r="H144" t="n">
-        <v>1</v>
-      </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J144" t="n">
-        <v>6.123233995736766e-17</v>
+        <v>-1.83697019872103e-16</v>
       </c>
       <c r="K144" t="n">
-        <v>1800</v>
+        <v>7600</v>
       </c>
       <c r="L144" t="n">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="M144" t="n">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="N144" t="n">
-        <v>2166.666666666667</v>
+        <v>3600</v>
       </c>
       <c r="O144" t="n">
-        <v>2650</v>
+        <v>3250</v>
       </c>
       <c r="P144" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="Q144" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="R144" t="n">
-        <v>21.66666666666667</v>
+        <v>36</v>
       </c>
       <c r="S144" t="n">
-        <v>79</v>
+        <v>-48</v>
       </c>
       <c r="T144" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -9426,61 +9372,61 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="E145" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F145" t="n">
+        <v>50</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>45230</v>
+      </c>
+      <c r="H145" t="n">
         <v>4</v>
       </c>
-      <c r="D145" s="2" t="n">
-        <v>45412</v>
-      </c>
-      <c r="E145" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F145" t="n">
-        <v>52</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>45412</v>
-      </c>
-      <c r="H145" t="n">
-        <v>2</v>
-      </c>
       <c r="I145" t="n">
-        <v>0.8660254037844387</v>
+        <v>-0.8660254037844386</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.4999999999999998</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K145" t="n">
-        <v>9700</v>
+        <v>2800</v>
       </c>
       <c r="L145" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="M145" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="N145" t="n">
-        <v>4466.666666666667</v>
+        <v>4166.666666666667</v>
       </c>
       <c r="O145" t="n">
-        <v>3800</v>
+        <v>3116.666666666667</v>
       </c>
       <c r="P145" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="Q145" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R145" t="n">
-        <v>44.66666666666666</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="S145" t="n">
-        <v>-45</v>
+        <v>22</v>
       </c>
       <c r="T145" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
@@ -9490,61 +9436,61 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>45443</v>
+        <v>45260</v>
       </c>
       <c r="E146" t="n">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="F146" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>45443</v>
+        <v>45260</v>
       </c>
       <c r="H146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.8660254037844387</v>
+        <v>0.8660254037844384</v>
       </c>
       <c r="K146" t="n">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="L146" t="n">
-        <v>1800</v>
+        <v>7600</v>
       </c>
       <c r="M146" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="N146" t="n">
-        <v>5566.666666666667</v>
+        <v>5133.333333333333</v>
       </c>
       <c r="O146" t="n">
-        <v>3833.333333333333</v>
+        <v>3533.333333333333</v>
       </c>
       <c r="P146" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q146" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="R146" t="n">
-        <v>55.66666666666666</v>
+        <v>51.33333333333334</v>
       </c>
       <c r="S146" t="n">
-        <v>-29</v>
+        <v>-34</v>
       </c>
       <c r="T146" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
@@ -9554,61 +9500,61 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>45473</v>
+        <v>45291</v>
       </c>
       <c r="E147" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="F147" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>45473</v>
+        <v>45291</v>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>1.224646799147353e-16</v>
+        <v>-2.449293598294706e-16</v>
       </c>
       <c r="J147" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="L147" t="n">
-        <v>9700</v>
+        <v>2800</v>
       </c>
       <c r="M147" t="n">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="N147" t="n">
-        <v>5733.333333333333</v>
+        <v>3133.333333333333</v>
       </c>
       <c r="O147" t="n">
-        <v>3950</v>
+        <v>3366.666666666667</v>
       </c>
       <c r="P147" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q147" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="R147" t="n">
-        <v>57.33333333333334</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="S147" t="n">
-        <v>-10</v>
+        <v>12</v>
       </c>
       <c r="T147" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
@@ -9621,58 +9567,58 @@
         <v>2024</v>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>45504</v>
+        <v>45322</v>
       </c>
       <c r="E148" t="n">
-        <v>7300</v>
+        <v>1900</v>
       </c>
       <c r="F148" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>45504</v>
+        <v>45322</v>
       </c>
       <c r="H148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.4999999999999997</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.8660254037844388</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="K148" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="L148" t="n">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="M148" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="N148" t="n">
-        <v>2933.333333333333</v>
+        <v>3133.333333333333</v>
       </c>
       <c r="O148" t="n">
-        <v>3700</v>
+        <v>3650</v>
       </c>
       <c r="P148" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q148" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R148" t="n">
-        <v>29.33333333333333</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="S148" t="n">
-        <v>60</v>
+        <v>-9</v>
       </c>
       <c r="T148" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149">
@@ -9685,58 +9631,58 @@
         <v>2024</v>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>45535</v>
+        <v>45351</v>
       </c>
       <c r="E149" t="n">
-        <v>9200</v>
+        <v>1800</v>
       </c>
       <c r="F149" t="n">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>45535</v>
+        <v>45351</v>
       </c>
       <c r="H149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.8660254037844385</v>
+        <v>0.8660254037844386</v>
       </c>
       <c r="J149" t="n">
-        <v>-0.5000000000000004</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K149" t="n">
-        <v>7300</v>
+        <v>1900</v>
       </c>
       <c r="L149" t="n">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="M149" t="n">
-        <v>1800</v>
+        <v>7600</v>
       </c>
       <c r="N149" t="n">
-        <v>3633.333333333333</v>
+        <v>2100</v>
       </c>
       <c r="O149" t="n">
-        <v>4600</v>
+        <v>3616.666666666667</v>
       </c>
       <c r="P149" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="Q149" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R149" t="n">
-        <v>36.33333333333334</v>
+        <v>21</v>
       </c>
       <c r="S149" t="n">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="T149" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150">
@@ -9749,58 +9695,58 @@
         <v>2024</v>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>45565</v>
+        <v>45382</v>
       </c>
       <c r="E150" t="n">
-        <v>2400</v>
+        <v>9700</v>
       </c>
       <c r="F150" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>45565</v>
+        <v>45382</v>
       </c>
       <c r="H150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.83697019872103e-16</v>
+        <v>6.123233995736766e-17</v>
       </c>
       <c r="K150" t="n">
-        <v>9200</v>
+        <v>1800</v>
       </c>
       <c r="L150" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="M150" t="n">
-        <v>9700</v>
+        <v>2800</v>
       </c>
       <c r="N150" t="n">
-        <v>5933.333333333333</v>
+        <v>2166.666666666667</v>
       </c>
       <c r="O150" t="n">
-        <v>5833.333333333333</v>
+        <v>2650</v>
       </c>
       <c r="P150" t="n">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="Q150" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R150" t="n">
-        <v>59.33333333333334</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="S150" t="n">
-        <v>-68</v>
+        <v>79</v>
       </c>
       <c r="T150" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151">
@@ -9813,58 +9759,58 @@
         <v>2024</v>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>45596</v>
+        <v>45412</v>
       </c>
       <c r="E151" t="n">
-        <v>6700</v>
+        <v>5200</v>
       </c>
       <c r="F151" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>45596</v>
+        <v>45412</v>
       </c>
       <c r="H151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8660254037844386</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="J151" t="n">
-        <v>0.5000000000000001</v>
+        <v>-0.4999999999999998</v>
       </c>
       <c r="K151" t="n">
-        <v>2400</v>
+        <v>9700</v>
       </c>
       <c r="L151" t="n">
-        <v>7300</v>
+        <v>1900</v>
       </c>
       <c r="M151" t="n">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="N151" t="n">
-        <v>6300</v>
+        <v>4466.666666666667</v>
       </c>
       <c r="O151" t="n">
-        <v>4616.666666666667</v>
+        <v>3800</v>
       </c>
       <c r="P151" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="Q151" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="R151" t="n">
-        <v>63</v>
+        <v>44.66666666666666</v>
       </c>
       <c r="S151" t="n">
-        <v>29</v>
+        <v>-45</v>
       </c>
       <c r="T151" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
@@ -9877,58 +9823,58 @@
         <v>2024</v>
       </c>
       <c r="C152" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>45626</v>
+        <v>45443</v>
       </c>
       <c r="E152" t="n">
-        <v>10800</v>
+        <v>2300</v>
       </c>
       <c r="F152" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>45626</v>
+        <v>45443</v>
       </c>
       <c r="H152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.5000000000000004</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>0.8660254037844384</v>
+        <v>-0.8660254037844387</v>
       </c>
       <c r="K152" t="n">
-        <v>6700</v>
+        <v>5200</v>
       </c>
       <c r="L152" t="n">
-        <v>9200</v>
+        <v>1800</v>
       </c>
       <c r="M152" t="n">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="N152" t="n">
-        <v>6100</v>
+        <v>5566.666666666667</v>
       </c>
       <c r="O152" t="n">
-        <v>4866.666666666667</v>
+        <v>3833.333333333333</v>
       </c>
       <c r="P152" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q152" t="n">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="R152" t="n">
-        <v>56.33333333333334</v>
+        <v>55.66666666666666</v>
       </c>
       <c r="S152" t="n">
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="T152" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153">
@@ -9941,58 +9887,58 @@
         <v>2024</v>
       </c>
       <c r="C153" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>45657</v>
+        <v>45473</v>
       </c>
       <c r="E153" t="n">
-        <v>8400</v>
+        <v>1300</v>
       </c>
       <c r="F153" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>45657</v>
+        <v>45473</v>
       </c>
       <c r="H153" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
-        <v>-2.449293598294706e-16</v>
+        <v>1.224646799147353e-16</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K153" t="n">
-        <v>10800</v>
+        <v>2300</v>
       </c>
       <c r="L153" t="n">
-        <v>2400</v>
+        <v>9700</v>
       </c>
       <c r="M153" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="N153" t="n">
-        <v>6633.333333333333</v>
+        <v>5733.333333333333</v>
       </c>
       <c r="O153" t="n">
-        <v>6283.333333333333</v>
+        <v>3950</v>
       </c>
       <c r="P153" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="Q153" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="R153" t="n">
-        <v>37.66666666666666</v>
+        <v>57.33333333333334</v>
       </c>
       <c r="S153" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="T153" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154">
@@ -10002,61 +9948,61 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>45688</v>
+        <v>45504</v>
       </c>
       <c r="E154" t="n">
-        <v>9000</v>
+        <v>7300</v>
       </c>
       <c r="F154" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>45688</v>
+        <v>45504</v>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.4999999999999997</v>
       </c>
       <c r="J154" t="n">
-        <v>0.8660254037844387</v>
+        <v>-0.8660254037844388</v>
       </c>
       <c r="K154" t="n">
-        <v>8400</v>
+        <v>1300</v>
       </c>
       <c r="L154" t="n">
-        <v>6700</v>
+        <v>5200</v>
       </c>
       <c r="M154" t="n">
-        <v>7300</v>
+        <v>1900</v>
       </c>
       <c r="N154" t="n">
-        <v>8633.333333333334</v>
+        <v>2933.333333333333</v>
       </c>
       <c r="O154" t="n">
-        <v>7466.666666666667</v>
+        <v>3700</v>
       </c>
       <c r="P154" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Q154" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R154" t="n">
-        <v>39</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="S154" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="T154" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="155">
@@ -10066,61 +10012,61 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>45716</v>
+        <v>45535</v>
       </c>
       <c r="E155" t="n">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="F155" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>45716</v>
+        <v>45535</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I155" t="n">
-        <v>0.8660254037844386</v>
+        <v>-0.8660254037844385</v>
       </c>
       <c r="J155" t="n">
-        <v>0.5000000000000001</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="K155" t="n">
-        <v>9000</v>
+        <v>7300</v>
       </c>
       <c r="L155" t="n">
-        <v>10800</v>
+        <v>2300</v>
       </c>
       <c r="M155" t="n">
-        <v>9200</v>
+        <v>1800</v>
       </c>
       <c r="N155" t="n">
-        <v>9400</v>
+        <v>3633.333333333333</v>
       </c>
       <c r="O155" t="n">
-        <v>7750</v>
+        <v>4600</v>
       </c>
       <c r="P155" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="Q155" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R155" t="n">
-        <v>31.33333333333333</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T155" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156">
@@ -10130,61 +10076,61 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C156" t="n">
+        <v>9</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F156" t="n">
+        <v>24</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>45565</v>
+      </c>
+      <c r="H156" t="n">
         <v>3</v>
       </c>
-      <c r="D156" s="2" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E156" t="n">
-        <v>8100</v>
-      </c>
-      <c r="F156" t="n">
-        <v>27</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>45747</v>
-      </c>
-      <c r="H156" t="n">
-        <v>1</v>
-      </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J156" t="n">
-        <v>6.123233995736766e-17</v>
+        <v>-1.83697019872103e-16</v>
       </c>
       <c r="K156" t="n">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="L156" t="n">
-        <v>8400</v>
+        <v>1300</v>
       </c>
       <c r="M156" t="n">
-        <v>2400</v>
+        <v>9700</v>
       </c>
       <c r="N156" t="n">
-        <v>8800</v>
+        <v>5933.333333333333</v>
       </c>
       <c r="O156" t="n">
-        <v>7716.666666666667</v>
+        <v>5833.333333333333</v>
       </c>
       <c r="P156" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="Q156" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R156" t="n">
-        <v>29.33333333333333</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="S156" t="n">
-        <v>-3</v>
+        <v>-68</v>
       </c>
       <c r="T156" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157">
@@ -10194,61 +10140,61 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C157" t="n">
+        <v>10</v>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="E157" t="n">
+        <v>6700</v>
+      </c>
+      <c r="F157" t="n">
+        <v>53</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="H157" t="n">
         <v>4</v>
       </c>
-      <c r="D157" s="2" t="n">
-        <v>45777</v>
-      </c>
-      <c r="E157" t="n">
-        <v>6900</v>
-      </c>
-      <c r="F157" t="n">
-        <v>23</v>
-      </c>
-      <c r="G157" s="3" t="n">
-        <v>45777</v>
-      </c>
-      <c r="H157" t="n">
-        <v>2</v>
-      </c>
       <c r="I157" t="n">
-        <v>0.8660254037844387</v>
+        <v>-0.8660254037844386</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.4999999999999998</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K157" t="n">
-        <v>8100</v>
+        <v>2400</v>
       </c>
       <c r="L157" t="n">
-        <v>9000</v>
+        <v>7300</v>
       </c>
       <c r="M157" t="n">
-        <v>6700</v>
+        <v>5200</v>
       </c>
       <c r="N157" t="n">
-        <v>8700</v>
+        <v>6300</v>
       </c>
       <c r="O157" t="n">
-        <v>8666.666666666666</v>
+        <v>4616.666666666667</v>
       </c>
       <c r="P157" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q157" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="R157" t="n">
+        <v>63</v>
+      </c>
+      <c r="S157" t="n">
         <v>29</v>
       </c>
-      <c r="S157" t="n">
-        <v>-4</v>
-      </c>
       <c r="T157" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158">
@@ -10258,61 +10204,61 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>45808</v>
+        <v>45626</v>
       </c>
       <c r="E158" t="n">
-        <v>4500</v>
+        <v>10800</v>
       </c>
       <c r="F158" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>45808</v>
+        <v>45626</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4999999999999999</v>
+        <v>-0.5000000000000004</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.8660254037844387</v>
+        <v>0.8660254037844384</v>
       </c>
       <c r="K158" t="n">
-        <v>6900</v>
+        <v>6700</v>
       </c>
       <c r="L158" t="n">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="M158" t="n">
-        <v>10800</v>
+        <v>2300</v>
       </c>
       <c r="N158" t="n">
-        <v>8000</v>
+        <v>6100</v>
       </c>
       <c r="O158" t="n">
-        <v>8700</v>
+        <v>4866.666666666667</v>
       </c>
       <c r="P158" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="Q158" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="R158" t="n">
-        <v>26.66666666666667</v>
+        <v>56.33333333333334</v>
       </c>
       <c r="S158" t="n">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="T158" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="159">
@@ -10322,61 +10268,61 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="E159" t="n">
-        <v>5100</v>
+        <v>8400</v>
       </c>
       <c r="F159" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="H159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I159" t="n">
-        <v>1.224646799147353e-16</v>
+        <v>-2.449293598294706e-16</v>
       </c>
       <c r="J159" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>4500</v>
+        <v>10800</v>
       </c>
       <c r="L159" t="n">
-        <v>8100</v>
+        <v>2400</v>
       </c>
       <c r="M159" t="n">
-        <v>8400</v>
+        <v>1300</v>
       </c>
       <c r="N159" t="n">
-        <v>6500</v>
+        <v>6633.333333333333</v>
       </c>
       <c r="O159" t="n">
-        <v>7650</v>
+        <v>6283.333333333333</v>
       </c>
       <c r="P159" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="Q159" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R159" t="n">
-        <v>21.66666666666667</v>
+        <v>37.66666666666666</v>
       </c>
       <c r="S159" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="T159" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160">
@@ -10389,58 +10335,58 @@
         <v>2025</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>45869</v>
+        <v>45688</v>
       </c>
       <c r="E160" t="n">
-        <v>5100</v>
+        <v>9000</v>
       </c>
       <c r="F160" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>45869</v>
+        <v>45688</v>
       </c>
       <c r="H160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4999999999999997</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.8660254037844388</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="K160" t="n">
-        <v>5100</v>
+        <v>8400</v>
       </c>
       <c r="L160" t="n">
-        <v>6900</v>
+        <v>6700</v>
       </c>
       <c r="M160" t="n">
-        <v>9000</v>
+        <v>7300</v>
       </c>
       <c r="N160" t="n">
-        <v>5500</v>
+        <v>8633.333333333334</v>
       </c>
       <c r="O160" t="n">
-        <v>7100</v>
+        <v>7466.666666666667</v>
       </c>
       <c r="P160" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Q160" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="R160" t="n">
-        <v>18.33333333333333</v>
+        <v>39</v>
       </c>
       <c r="S160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T160" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161">
@@ -10453,58 +10399,58 @@
         <v>2025</v>
       </c>
       <c r="C161" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>45900</v>
+        <v>45716</v>
       </c>
       <c r="E161" t="n">
-        <v>3900</v>
+        <v>9000</v>
       </c>
       <c r="F161" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>45900</v>
+        <v>45716</v>
       </c>
       <c r="H161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8660254037844385</v>
+        <v>0.8660254037844386</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.5000000000000004</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="K161" t="n">
-        <v>5100</v>
+        <v>9000</v>
       </c>
       <c r="L161" t="n">
-        <v>4500</v>
+        <v>10800</v>
       </c>
       <c r="M161" t="n">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="N161" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="O161" t="n">
-        <v>6450</v>
+        <v>7750</v>
       </c>
       <c r="P161" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="Q161" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="R161" t="n">
-        <v>16.33333333333333</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="S161" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162">
@@ -10517,58 +10463,58 @@
         <v>2025</v>
       </c>
       <c r="C162" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>45930</v>
+        <v>45747</v>
       </c>
       <c r="E162" t="n">
-        <v>4200</v>
+        <v>8100</v>
       </c>
       <c r="F162" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>45930</v>
+        <v>45747</v>
       </c>
       <c r="H162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.83697019872103e-16</v>
+        <v>6.123233995736766e-17</v>
       </c>
       <c r="K162" t="n">
-        <v>3900</v>
+        <v>9000</v>
       </c>
       <c r="L162" t="n">
-        <v>5100</v>
+        <v>8400</v>
       </c>
       <c r="M162" t="n">
-        <v>8100</v>
+        <v>2400</v>
       </c>
       <c r="N162" t="n">
-        <v>4700</v>
+        <v>8800</v>
       </c>
       <c r="O162" t="n">
-        <v>5600</v>
+        <v>7716.666666666667</v>
       </c>
       <c r="P162" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="Q162" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="R162" t="n">
-        <v>15.66666666666667</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="T162" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163">
@@ -10581,58 +10527,58 @@
         <v>2025</v>
       </c>
       <c r="C163" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>45961</v>
+        <v>45777</v>
       </c>
       <c r="E163" t="n">
-        <v>4800</v>
+        <v>6900</v>
       </c>
       <c r="F163" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>45961</v>
+        <v>45777</v>
       </c>
       <c r="H163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.8660254037844386</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="J163" t="n">
-        <v>0.5000000000000001</v>
+        <v>-0.4999999999999998</v>
       </c>
       <c r="K163" t="n">
-        <v>4200</v>
+        <v>8100</v>
       </c>
       <c r="L163" t="n">
-        <v>5100</v>
+        <v>9000</v>
       </c>
       <c r="M163" t="n">
-        <v>6900</v>
+        <v>6700</v>
       </c>
       <c r="N163" t="n">
-        <v>4400</v>
+        <v>8700</v>
       </c>
       <c r="O163" t="n">
-        <v>4950</v>
+        <v>8666.666666666666</v>
       </c>
       <c r="P163" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Q163" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="R163" t="n">
-        <v>14.66666666666667</v>
+        <v>29</v>
       </c>
       <c r="S163" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="T163" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="164">
@@ -10645,58 +10591,58 @@
         <v>2025</v>
       </c>
       <c r="C164" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>45991</v>
+        <v>45808</v>
       </c>
       <c r="E164" t="n">
-        <v>7800</v>
+        <v>4500</v>
       </c>
       <c r="F164" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>45991</v>
+        <v>45808</v>
       </c>
       <c r="H164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.5000000000000004</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>0.8660254037844384</v>
+        <v>-0.8660254037844387</v>
       </c>
       <c r="K164" t="n">
-        <v>4800</v>
+        <v>6900</v>
       </c>
       <c r="L164" t="n">
-        <v>3900</v>
+        <v>9000</v>
       </c>
       <c r="M164" t="n">
-        <v>4500</v>
+        <v>10800</v>
       </c>
       <c r="N164" t="n">
-        <v>4300</v>
+        <v>8000</v>
       </c>
       <c r="O164" t="n">
-        <v>4600</v>
+        <v>8700</v>
       </c>
       <c r="P164" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q164" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R164" t="n">
-        <v>14.33333333333333</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="T164" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="165">
@@ -10709,57 +10655,441 @@
         <v>2025</v>
       </c>
       <c r="C165" t="n">
+        <v>6</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E165" t="n">
+        <v>5100</v>
+      </c>
+      <c r="F165" t="n">
+        <v>17</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>45838</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L165" t="n">
+        <v>8100</v>
+      </c>
+      <c r="M165" t="n">
+        <v>8400</v>
+      </c>
+      <c r="N165" t="n">
+        <v>6500</v>
+      </c>
+      <c r="O165" t="n">
+        <v>7650</v>
+      </c>
+      <c r="P165" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>27</v>
+      </c>
+      <c r="R165" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="S165" t="n">
+        <v>2</v>
+      </c>
+      <c r="T165" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Légalisation</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="E166" t="n">
+        <v>5100</v>
+      </c>
+      <c r="F166" t="n">
+        <v>17</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J166" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K166" t="n">
+        <v>5100</v>
+      </c>
+      <c r="L166" t="n">
+        <v>6900</v>
+      </c>
+      <c r="M166" t="n">
+        <v>9000</v>
+      </c>
+      <c r="N166" t="n">
+        <v>5500</v>
+      </c>
+      <c r="O166" t="n">
+        <v>7100</v>
+      </c>
+      <c r="P166" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>23</v>
+      </c>
+      <c r="R166" t="n">
+        <v>18.33333333333333</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Légalisation</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C167" t="n">
+        <v>8</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="E167" t="n">
+        <v>3900</v>
+      </c>
+      <c r="F167" t="n">
+        <v>13</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>45900</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J167" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K167" t="n">
+        <v>5100</v>
+      </c>
+      <c r="L167" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M167" t="n">
+        <v>9000</v>
+      </c>
+      <c r="N167" t="n">
+        <v>4900</v>
+      </c>
+      <c r="O167" t="n">
+        <v>6450</v>
+      </c>
+      <c r="P167" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>15</v>
+      </c>
+      <c r="R167" t="n">
+        <v>16.33333333333333</v>
+      </c>
+      <c r="S167" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T167" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Légalisation</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C168" t="n">
+        <v>9</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E168" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F168" t="n">
+        <v>14</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K168" t="n">
+        <v>3900</v>
+      </c>
+      <c r="L168" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M168" t="n">
+        <v>8100</v>
+      </c>
+      <c r="N168" t="n">
+        <v>4700</v>
+      </c>
+      <c r="O168" t="n">
+        <v>5600</v>
+      </c>
+      <c r="P168" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>17</v>
+      </c>
+      <c r="R168" t="n">
+        <v>15.66666666666667</v>
+      </c>
+      <c r="S168" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Légalisation</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C169" t="n">
+        <v>10</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="E169" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F169" t="n">
+        <v>16</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="H169" t="n">
+        <v>4</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K169" t="n">
+        <v>4200</v>
+      </c>
+      <c r="L169" t="n">
+        <v>5100</v>
+      </c>
+      <c r="M169" t="n">
+        <v>6900</v>
+      </c>
+      <c r="N169" t="n">
+        <v>4400</v>
+      </c>
+      <c r="O169" t="n">
+        <v>4950</v>
+      </c>
+      <c r="P169" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>17</v>
+      </c>
+      <c r="R169" t="n">
+        <v>14.66666666666667</v>
+      </c>
+      <c r="S169" t="n">
+        <v>2</v>
+      </c>
+      <c r="T169" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Légalisation</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C170" t="n">
+        <v>11</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E170" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F170" t="n">
+        <v>26</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>45991</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K170" t="n">
+        <v>4800</v>
+      </c>
+      <c r="L170" t="n">
+        <v>3900</v>
+      </c>
+      <c r="M170" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N170" t="n">
+        <v>4300</v>
+      </c>
+      <c r="O170" t="n">
+        <v>4600</v>
+      </c>
+      <c r="P170" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>13</v>
+      </c>
+      <c r="R170" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Légalisation</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C171" t="n">
         <v>12</v>
       </c>
-      <c r="D165" s="2" t="n">
+      <c r="D171" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E171" t="n">
         <v>4800</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F171" t="n">
         <v>16</v>
       </c>
-      <c r="G165" s="3" t="n">
+      <c r="G171" s="3" t="n">
         <v>46022</v>
       </c>
-      <c r="H165" t="n">
+      <c r="H171" t="n">
         <v>4</v>
       </c>
-      <c r="I165" t="n">
+      <c r="I171" t="n">
         <v>-2.449293598294706e-16</v>
       </c>
-      <c r="J165" t="n">
-        <v>1</v>
-      </c>
-      <c r="K165" t="n">
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="n">
         <v>7800</v>
       </c>
-      <c r="L165" t="n">
+      <c r="L171" t="n">
         <v>4200</v>
       </c>
-      <c r="M165" t="n">
+      <c r="M171" t="n">
         <v>5100</v>
       </c>
-      <c r="N165" t="n">
+      <c r="N171" t="n">
         <v>5600</v>
       </c>
-      <c r="O165" t="n">
+      <c r="O171" t="n">
         <v>5150</v>
       </c>
-      <c r="P165" t="n">
+      <c r="P171" t="n">
         <v>26</v>
       </c>
-      <c r="Q165" t="n">
+      <c r="Q171" t="n">
         <v>14</v>
       </c>
-      <c r="R165" t="n">
+      <c r="R171" t="n">
         <v>18.66666666666667</v>
       </c>
-      <c r="S165" t="n">
+      <c r="S171" t="n">
         <v>-10</v>
       </c>
-      <c r="T165" t="n">
+      <c r="T171" t="n">
         <v>35</v>
       </c>
     </row>
